--- a/vulns_framework_mapping.xlsx
+++ b/vulns_framework_mapping.xlsx
@@ -1428,13 +1428,34 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>No Account Lockout Policy (threshold &gt; 5)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2
+CIS 6.5</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1.4.1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>8.3.4</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -3815,7 +3836,8 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Account Lockout Duration Not Configured Or Insufficient</t>
+          <t>Account Lockout Duration Not Configured Or Insufficient
+(threshold &gt; 5 → 27: Excessive Number Of Failed Login Attempts Allowed)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">

--- a/vulns_framework_mapping.xlsx
+++ b/vulns_framework_mapping.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Finding" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'By Vuln'!$A$1:$H$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'By Vuln'!$A$1:$H$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'By Finding'!$A$1:$G$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2499,8 +2499,81 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>User-ID Is Not Turned On / Configured</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>User-ID Not Configured</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.1</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>IAC-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Server Verification Disabled</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Update Server Verification Disabled</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.6
+CIS 12.6</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1.6.1</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>6.3.1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>VPM-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H60"/>
+  <autoFilter ref="A1:H62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4942,10 +5015,12 @@
           <t>Update Server Verification Disabled</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="n">
+        <v>61</v>
+      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>Server Verification Disabled</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5107,10 +5182,12 @@
           <t>User-ID Not Configured</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="n">
+        <v>60</v>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>User-ID Is Not Turned On / Configured</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">

--- a/vulns_framework_mapping.xlsx
+++ b/vulns_framework_mapping.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Vuln" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Finding" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Palo Alto Findings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check Point Findings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'By Vuln'!$A$1:$H$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'By Finding'!$A$1:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'By Vuln'!$A$1:$N$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Palo Alto Findings'!$A$1:$H$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Check Point Findings'!$A$1:$H$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,17 +434,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,32 +466,62 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t># Findings</t>
+          <t># PA Findings</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>PA Analyzer Findings</t>
+          <t>Palo Alto Findings</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>CIS Controls v8</t>
+          <t>PA CIS Controls v8</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CIS PAN-OS Benchmark</t>
+          <t>PA CIS Benchmark</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>PCI DSS v4.0</t>
+          <t>PA PCI DSS v4.0</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>SCF</t>
+          <t>PA SCF</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t># CP Findings</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Check Point Findings</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CP CIS Controls v8</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>CP CIS Benchmark</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CP PCI DSS v4.0</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>CP SCF</t>
         </is>
       </c>
     </row>
@@ -520,6 +558,14 @@
           <t>OPS-01</t>
         </is>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -560,6 +606,14 @@
           <t>IAC-06</t>
         </is>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -578,6 +632,14 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -596,6 +658,30 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.8 — Ensure Host Name is set</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2.1.8</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -618,6 +704,31 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.4 — Ensure Hit count is Enable for the rules
+No Hit Count Data</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -636,6 +747,14 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -672,6 +791,14 @@
 OPS-01</t>
         </is>
       </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -715,6 +842,14 @@
 VPM-10</t>
         </is>
       </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -760,6 +895,14 @@
 IAC-10</t>
         </is>
       </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -795,6 +938,34 @@
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.13 — Ensure Allow access again after time is set to 300 or more seconds</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8.2.8</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>IAC-06</t>
         </is>
@@ -817,6 +988,14 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -856,6 +1035,30 @@
           <t>IAC-06</t>
         </is>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.4 — Ensure Check for Password Reuse is selected and History Length is set to 12 or more - history-checking</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -892,6 +1095,36 @@
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.5 — Ensure Password Expiration is set to 90 days
+CIS 1.6 — Ensure Warn users before password expiration is set to 7 days
+CIS 1.7 — Ensure Lockout users after password expiration is set to 1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2
+CIS 5.3</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1.5
+1.6
+1.7</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06
+IAC-07</t>
         </is>
       </c>
     </row>
@@ -912,6 +1145,14 @@
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -946,6 +1187,30 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.1 — Ensure Minimum Password Length is set to 14 or higher</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>IAC-06</t>
         </is>
@@ -968,6 +1233,14 @@
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1006,6 +1279,41 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.14 — Ensure Accept RIP is not enabled
+CIS 3.15 — Ensure Accept Domain Name over TCP (Zone Transfer) is not enabled
+CIS 3.16 — Ensure Accept Domain Name over UDP (Queries) is not enabled
+CIS 3.17 — Ensure Accept ICMP Requests is not enabled</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8
+CIS 13.4</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3.14
+3.15
+3.16
+3.17</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1044,6 +1352,14 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1090,6 +1406,14 @@
 TDA-02</t>
         </is>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1138,6 +1462,14 @@
 NET-04</t>
         </is>
       </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1177,6 +1509,14 @@
           <t>DAM-01</t>
         </is>
       </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1254,6 +1594,14 @@
 VPM-01</t>
         </is>
       </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1292,6 +1640,32 @@
           <t>IAC-09</t>
         </is>
       </c>
+      <c r="I24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.5.1 — Ensure CLI session timeout is set to less than or equal to 10 minutes
+CIS 2.5.2 — Ensure Web session timeout is set to less than or equal to 10 minutes</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.3</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2.5.1
+2.5.2</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>IAC-09</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1323,6 +1697,31 @@
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.2.4 — Ensure SNMP traps receivers is set</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2
+CIS 8.9</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>MON-06</t>
         </is>
@@ -1375,6 +1774,35 @@
 NET-04</t>
         </is>
       </c>
+      <c r="I26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.5 — Ensure no Allow Rule with Any in Destination filed present in the Firewall Rules
+CIS 3.6 — Ensure no Allow Rule with Any in Source filed present in the Firewall Rules
+Rule Allows Any Source
+Rule Allows Any Destination</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2
+CIS 13.4</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3.5
+3.6</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1417,6 +1845,32 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="I27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.7 — Ensure no Allow Rule with Any in Services filed present in the Firewall Rules
+Rule Allows Any Service</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2
+CIS 13.4</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1452,6 +1906,36 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.11 — Ensure Deny access after failed login attempts is selected
+CIS 1.12 — Ensure Maximum number of failed attempts allowed is set to 5 or fewer</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1.11
+1.12</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8.2.8</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>IAC-06</t>
         </is>
@@ -1501,6 +1985,32 @@
           <t>IAC-06</t>
         </is>
       </c>
+      <c r="I29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.2 — Ensure Disallow Palindromes is selected
+CIS 1.3 — Ensure Password Complexity is set to 3</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1.2
+1.3</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1519,6 +2029,30 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.10 — Ensure Force users to change password at first login after password was changed from Users page is selected</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1537,6 +2071,14 @@
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1592,6 +2134,14 @@
 VPM-01</t>
         </is>
       </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1646,6 +2196,51 @@
         <is>
           <t>MON-06
 TDA-02</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.2.3 — Ensure SNMP traps is enabled - authorizationError
+CIS 2.6.1 — Ensure mgmtauditlogs is set to on
+CIS 2.6.2 — Ensure auditlog is set to permanent
+CIS 2.6.3 — Ensure cplogs is set to on
+CIS 3.8 — Logging should be enable for all Firewall Rules
+CIS 3.9 — Review and Log Implied Rules
+CIS 3.20 — Ensure Logging is enabled for Track Options of Global Properties
+Allow Rule Not Logging</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2
+CIS 8.2
+CIS 8.5
+CIS 12.2</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>2.2.3
+2.6.1
+2.6.2
+2.6.3
+3.8
+3.9
+3.20</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>10.2.2</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>MON-06
+NET-04</t>
         </is>
       </c>
     </row>
@@ -1690,6 +2285,14 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1725,6 +2328,14 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1759,6 +2370,14 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1793,6 +2412,26 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Disabled Rulebase Rule</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1827,6 +2466,31 @@
           <t>OPS-01</t>
         </is>
       </c>
+      <c r="I38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.3 — Use Checkpoint Sections and Titles
+Missing Rule Comment</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1862,6 +2526,14 @@
 MON-06</t>
         </is>
       </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1910,6 +2582,37 @@
 IAC-10</t>
         </is>
       </c>
+      <c r="I40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.8 — Ensure Deny access to unused accounts is selected
+CIS 1.9 — Ensure Days of non-use before lock-out is set to 30
+CIS 2.5.4 — Ensure Radius or TACACS+ server is configured - tacacs-servers state on</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.3
+CIS 6.5
+CIS 6.7</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>1.8
+1.9
+2.5.4</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>IAC-01
+IAC-07</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -1951,6 +2654,37 @@
         <is>
           <t>CRY-03
 NET-06</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.9 — Ensure Telnet is disabled
+CIS 2.5.3 — Ensure Client Authentication is secured.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8
+CIS 12.6</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>2.1.9
+2.5.3</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>CRY-03</t>
         </is>
       </c>
     </row>
@@ -1971,6 +2705,14 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -1989,6 +2731,14 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2007,6 +2757,35 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.5 — Ensure unused interfaces are disabled</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>2.1.5</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>1.2.1
+1.4.1</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2048,6 +2827,40 @@
         <is>
           <t>IAC-01
 NET-04</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.2 — Configure a Default Drop/Cleanup Rule
+No Default Drop/Cleanup Rule</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2
+CIS 13.4</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>1.2.1
+1.3.1
+1.4.1
+1.4.2
+1.4.3</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
         </is>
       </c>
     </row>
@@ -2068,6 +2881,14 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2086,6 +2907,30 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.2 — Ensure 'Message Of The Day (MOTD)' is set - motd banner on</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2.1.2</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>IAC-09</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2126,6 +2971,14 @@
 MON-06</t>
         </is>
       </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2164,6 +3017,30 @@
           <t>IAC-09</t>
         </is>
       </c>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.1 — Ensure 'Login Banner' is set - message banner on</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>IAC-09</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2198,6 +3075,14 @@
           <t>OPS-04</t>
         </is>
       </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2216,6 +3101,14 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2234,6 +3127,14 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2277,6 +3178,44 @@
 NET-04</t>
         </is>
       </c>
+      <c r="I53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.5.5 — Ensure allowed-client is set to those necessary for device management
+CIS 3.1 — Enable the Firewall Stealth Rule</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.7
+CIS 12.2
+CIS 12.3
+CIS 13.4</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>2.5.5
+3.1</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>1.2.1
+1.3.1
+1.4.1
+1.4.2
+1.4.3</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>IAC-10
+NET-04</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2310,6 +3249,39 @@
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>CRY-03
+NET-06</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.2.1 — Ensure SNMP agent is disabled
+CIS 2.2.2 — Ensure SNMP version is set to v3-Only</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8
+CIS 12.3
+CIS 12.6</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1
+2.2.2</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>CRY-03
 NET-06</t>
@@ -2333,6 +3305,14 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2363,6 +3343,30 @@
           <t>OPS-01</t>
         </is>
       </c>
+      <c r="I56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.6 — Ensure DNS server is configured - primary</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.9</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>2.1.6</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -2393,6 +3397,37 @@
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.3.1 — Ensure NTP is enabled and IP address is set for Primary and Secondary NTP server - ntp active</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.4</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>10.6
+10.6.1
+10.6.2
+10.6.3</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>OPS-01</t>
         </is>
@@ -2415,6 +3450,30 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.3.2 — Ensure timezone is properly configured</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.4</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2.3.2</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -2462,6 +3521,14 @@
 NET-04</t>
         </is>
       </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -2498,6 +3565,14 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -2532,6 +3607,14 @@
           <t>IAC-01</t>
         </is>
       </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -2571,9 +3654,17 @@
           <t>VPM-10</t>
         </is>
       </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H62"/>
+  <autoFilter ref="A1:N62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2584,22 +3675,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PA Analyzer Finding</t>
+          <t>Finding</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2630,6 +3722,11 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SCF</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
@@ -2664,9 +3761,10 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>VPM-10 · TDA-02</t>
-        </is>
-      </c>
+          <t>TDA-02 · VPM-10</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2698,6 +3796,7 @@
           <t>IAC-06</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2733,6 +3832,7 @@
           <t>CRY-03 · IAC-10</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2764,6 +3864,7 @@
           <t>IAC-01</t>
         </is>
       </c>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2796,9 +3897,10 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>TDA-02 · NET-14</t>
-        </is>
-      </c>
+          <t>NET-14 · TDA-02</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2830,6 +3932,7 @@
           <t>MON-06</t>
         </is>
       </c>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2865,6 +3968,7 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2897,9 +4001,10 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>TDA-02 · NET-14</t>
-        </is>
-      </c>
+          <t>NET-14 · TDA-02</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2935,6 +4040,7 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2970,6 +4076,7 @@
           <t>TDA-02 · VPM-01</t>
         </is>
       </c>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3001,6 +4108,7 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3032,6 +4140,7 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3063,6 +4172,7 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3090,6 +4200,7 @@
           <t>OPS-01</t>
         </is>
       </c>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3125,6 +4236,7 @@
           <t>DAM-01</t>
         </is>
       </c>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3160,6 +4272,7 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3195,6 +4308,7 @@
           <t>MON-06</t>
         </is>
       </c>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3226,6 +4340,7 @@
           <t>IAC-06</t>
         </is>
       </c>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3257,6 +4372,7 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3288,6 +4404,7 @@
           <t>IAC-07</t>
         </is>
       </c>
+      <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3316,9 +4433,10 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>NET-04 · IAC-10</t>
-        </is>
-      </c>
+          <t>IAC-10 · NET-04</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3350,6 +4468,7 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3385,6 +4504,7 @@
           <t>CRY-03 · NET-06</t>
         </is>
       </c>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3416,6 +4536,7 @@
           <t>OPS-04</t>
         </is>
       </c>
+      <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3451,6 +4572,7 @@
           <t>MON-06</t>
         </is>
       </c>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3482,6 +4604,7 @@
           <t>CRY-01</t>
         </is>
       </c>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3513,6 +4636,7 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3544,6 +4668,7 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3575,6 +4700,7 @@
           <t>NET-14</t>
         </is>
       </c>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3606,6 +4732,7 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3641,6 +4768,7 @@
           <t>IAC-06</t>
         </is>
       </c>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3676,6 +4804,7 @@
           <t>IAC-09</t>
         </is>
       </c>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3693,7 +4822,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.3 · CIS 6.7</t>
+          <t>CIS 6.7 · CIS 12.3</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3708,9 +4837,10 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>NET-04 · IAC-10</t>
-        </is>
-      </c>
+          <t>IAC-10 · NET-04</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3742,6 +4872,7 @@
           <t>OPS-01</t>
         </is>
       </c>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3773,6 +4904,7 @@
           <t>NET-14</t>
         </is>
       </c>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3801,9 +4933,10 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>OPS-01 · CRY-03</t>
-        </is>
-      </c>
+          <t>CRY-03 · OPS-01</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3835,6 +4968,7 @@
           <t>OPS-01</t>
         </is>
       </c>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3866,6 +5000,7 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3897,6 +5032,7 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3909,8 +5045,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Account Lockout Duration Not Configured Or Insufficient
-(threshold &gt; 5 → 27: Excessive Number Of Failed Login Attempts Allowed)</t>
+          <t>Account Lockout Duration Not Configured Or Insufficient</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3933,279 +5068,292 @@
           <t>IAC-06</t>
         </is>
       </c>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>No Default Deny Rule</t>
+          <t>No Account Lockout Policy (threshold &gt; 5)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Rules Allowing Excessive Traffic</t>
+          <t>Excessive Number Of Failed Login Attempts Allowed</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>CIS 5.2 · CIS 6.5</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1.4.1</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>8.3.4</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>per-finding override</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>No Logging Configured</t>
+          <t>No Default Deny Rule</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Insufficient Logging And Auditing</t>
+          <t>Rules Allowing Excessive Traffic</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2 · CIS 8.5</t>
+          <t>CIS 12.2 · CIS 13.4</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10.2.1 · 10.2.2</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
-        </is>
-      </c>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>No Login Banner</t>
+          <t>No Logging Configured</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Pre Login Banner Not Set</t>
+          <t>Insufficient Logging And Auditing</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>1.1.2</t>
-        </is>
-      </c>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>10.2.1 · 10.2.2</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
-        </is>
-      </c>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>No Management IP Restrictions</t>
+          <t>No Login Banner</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>WAN Management Access</t>
+          <t>Pre Login Banner Not Set</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.3 · CIS 6.7</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1.1.2</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>NET-04 · IAC-10</t>
-        </is>
-      </c>
+          <t>IAC-09</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>No Syslog Servers Configured</t>
+          <t>No Management IP Restrictions</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Missing Centralized Logging and Reporting</t>
+          <t>WAN Management Access</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2 · CIS 8.9</t>
+          <t>CIS 6.7 · CIS 12.3</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10.5.4</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
-        </is>
-      </c>
+          <t>IAC-10 · NET-04</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Only One NTP Server</t>
+          <t>No Syslog Servers Configured</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Secondary Ntp Server Not Configured</t>
+          <t>Missing Centralized Logging and Reporting</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.4</t>
+          <t>CIS 8.2 · CIS 8.9</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10.6.1</t>
+          <t>10.5.4</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
-        </is>
-      </c>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Packet-Based Attack Protection Disabled</t>
+          <t>Only One NTP Server</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Threat Protection Missing Or Not Configured</t>
+          <t>Secondary Ntp Server Not Configured</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CIS 13.3 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>6.18</t>
-        </is>
-      </c>
+          <t>CIS 8.4</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>10.6.1</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
-        </is>
-      </c>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Password Complexity Not Enforced</t>
+          <t>Packet-Based Attack Protection Disabled</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Password Complexity Requirements Not Enforced</t>
+          <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2</t>
+          <t>CIS 13.3 · CIS 13.4</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>1.3.1 · 1.3.3 · 1.3.4 · 1.3.5 · 1.3.6</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>8.3.6</t>
+          <t>1.2.4 · 1.3.1</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
-        </is>
-      </c>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Password Expiry Not Configured</t>
+          <t>Password Complexity Not Enforced</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Maximum password age</t>
+          <t>Password Complexity Requirements Not Enforced</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4215,12 +5363,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.1 · 1.3.3 · 1.3.4 · 1.3.5 · 1.3.6</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8.3.9</t>
+          <t>8.3.6</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -4228,34 +5376,35 @@
           <t>IAC-06</t>
         </is>
       </c>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Password Profile Bypass Configured</t>
+          <t>Password Expiry Not Configured</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Password Complexity Requirements Not Enforced</t>
+          <t>Maximum password age</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2 · CIS 6.5</t>
+          <t>CIS 5.2</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1.3.10</t>
+          <t>1.3.7</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>8.3.6</t>
+          <t>8.3.9</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4263,65 +5412,67 @@
           <t>IAC-06</t>
         </is>
       </c>
+      <c r="H51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Potential Shadow Rule</t>
+          <t>Password Profile Bypass Configured</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Shadow Firewall Rule / ACL</t>
+          <t>Password Complexity Requirements Not Enforced</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.2</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
+          <t>CIS 5.2 · CIS 6.5</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1.3.10</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>8.3.6</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
-        </is>
-      </c>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Reconnaissance Protection Disabled</t>
+          <t>Potential Shadow Rule</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Threat Protection Missing Or Not Configured</t>
+          <t>Shadow Firewall Rule / ACL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>CIS 13.3 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>6.17</t>
-        </is>
-      </c>
+          <t>CIS 4.2 · CIS 12.2</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4329,92 +5480,99 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Risky Application Allowed Without User-ID Restriction</t>
+          <t>Reconnaissance Protection Disabled</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Weak Authentication Configuration</t>
+          <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 4.2</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>CIS 13.3 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>6.17</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>7.2.1 · 8.2.1</t>
+          <t>1.2.4 · 1.3.1</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>IAC-01 · IAC-10</t>
-        </is>
-      </c>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SMB Exposed from Any Source</t>
+          <t>Risky Application Allowed Without User-ID Restriction</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
+          <t>Weak Authentication Configuration</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>CIS 4.2 · CIS 12.2</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>7.2.1 · 8.2.1</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
-        </is>
-      </c>
+          <t>IAC-01 · IAC-10</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SNMP Enabled Without Source Restrictions</t>
+          <t>SMB Exposed from Any Source</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>WAN Management Access</t>
+          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.3 · CIS 6.7</t>
+          <t>CIS 12.2 · CIS 13.4</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -4422,42 +5580,44 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SNMPv1 Enabled</t>
+          <t>SNMP Enabled Without Source Restrictions</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SNMPv1 Or SNMPv2 Enabled</t>
+          <t>WAN Management Access</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.3 · CIS 12.6</t>
+          <t>CIS 6.7 · CIS 12.3</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>NET-06 · CRY-03</t>
-        </is>
-      </c>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SNMPv2c Enabled</t>
+          <t>SNMPv1 Enabled</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -4470,7 +5630,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.3</t>
+          <t>CIS 4.2 · CIS 12.3 · CIS 12.6</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -4481,34 +5641,31 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>NET-06 · CRY-03</t>
-        </is>
-      </c>
+          <t>CRY-03 · NET-06</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SNMPv3 Polling Not Configured</t>
+          <t>SNMPv2c Enabled</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>SNMPv3 Query Per User</t>
+          <t>SNMPv1 Or SNMPv2 Enabled</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2 · CIS 8.9</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
-        </is>
-      </c>
+          <t>CIS 4.2 · CIS 12.3</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -4516,22 +5673,23 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>MON-06 · CRY-03</t>
-        </is>
-      </c>
+          <t>CRY-03 · NET-06</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SNMPv3 Trap Not Configured</t>
+          <t>SNMPv3 Polling Not Configured</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Insufficient Logging And Auditing</t>
+          <t>SNMPv3 Query Per User</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4541,292 +5699,301 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1.1.1.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>10.2.1 · 10.5.4</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
-        </is>
-      </c>
+          <t>CRY-03 · MON-06</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SSH Exposed from Any Source</t>
+          <t>SNMPv3 Trap Not Configured</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
+          <t>Insufficient Logging And Auditing</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 12.3</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>CIS 8.2 · CIS 8.9</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1.1.1.2</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>10.2.1 · 10.5.4</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
-        </is>
-      </c>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SSL Decryption Not Configured</t>
+          <t>SSH Exposed from Any Source</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Threat Protection Missing Or Not Configured</t>
+          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>CIS 3.10 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
+          <t>CIS 12.2 · CIS 12.3</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · NET-14</t>
-        </is>
-      </c>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Service=Any with Specific Application</t>
+          <t>SSL Decryption Not Configured</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Rules Allowing Excessive Traffic (Any Application Or Any Service)</t>
+          <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>CIS 3.10 · CIS 13.4</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
-        </is>
-      </c>
+          <t>CRY-03 · NET-14</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Syslog Transmitted Over UDP</t>
+          <t>Service=Any with Specific Application</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Syslog Transmitted Over UDP</t>
+          <t>Rules Allowing Excessive Traffic (Any Application Or Any Service)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.9</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>10.5.4</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>MON-06 · CRY-03</t>
-        </is>
-      </c>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TLS Profile Using Default Certificate</t>
+          <t>Syslog Transmitted Over UDP</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Invalid Certificate Used</t>
+          <t>Syslog Transmitted Over UDP</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.6</t>
+          <t>CIS 8.9</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>10.5.4</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
-        </is>
-      </c>
+          <t>CRY-03 · MON-06</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Telnet Management Enabled</t>
+          <t>TLS Profile Using Default Certificate</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Insecure Protocol Use</t>
+          <t>Invalid Certificate Used</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.3 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>1.2.3</t>
-        </is>
-      </c>
+          <t>CIS 4.2 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2.2.4 · 2.2.7</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · NET-06</t>
-        </is>
-      </c>
+          <t>CRY-03</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Threat Intelligence Blocking Not Configured</t>
+          <t>Telnet Management Enabled</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Block Malicious Domain</t>
+          <t>Insecure Protocol Use</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.1 · CIS 13.4</t>
+          <t>CIS 4.2 · CIS 12.3 · CIS 12.6</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>2.2.4 · 2.2.7</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>NET-04 · TDA-02</t>
-        </is>
-      </c>
+          <t>CRY-03 · NET-06</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>URL Category Action Not Blocking</t>
+          <t>Threat Intelligence Blocking Not Configured</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>URL Filtering</t>
+          <t>Block Malicious Domain</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CIS 9.2 · CIS 13.4</t>
+          <t>CIS 10.1 · CIS 13.4</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
-        </is>
-      </c>
+          <t>NET-04 · TDA-02</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>URL Filtering Not Configured</t>
+          <t>URL Category Action Not Blocking</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -4844,7 +6011,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4857,100 +6024,107 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>URL Filtering Not Logging</t>
+          <t>URL Filtering Not Configured</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Insufficient Logging And Auditing</t>
+          <t>URL Filtering</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2 · CIS 9.2</t>
+          <t>CIS 9.2 · CIS 13.4</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>10.2.1</t>
+          <t>1.2.4 · 1.3.1</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
-        </is>
-      </c>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>URL Filtering Profile Not Applied</t>
+          <t>URL Filtering Not Logging</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>URL Filtering</t>
+          <t>Insufficient Logging And Auditing</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CIS 9.2 · CIS 13.4</t>
+          <t>CIS 8.2 · CIS 9.2</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>10.2.1</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
-        </is>
-      </c>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Unrestricted Destination Address</t>
+          <t>URL Filtering Profile Not Applied</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
+          <t>URL Filtering</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
+          <t>CIS 9.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1.3.2</t>
+          <t>1.2.4 · 1.3.1</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4958,11 +6132,12 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Unrestricted Source Address</t>
+          <t>Unrestricted Destination Address</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -4981,7 +6156,7 @@
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>1.3.2</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -4989,118 +6164,118 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Unused Security Rule (Policy Optimizer)</t>
+          <t>Unrestricted Source Address</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Unused Rule / Policy Enabled</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Update Server Verification Disabled</t>
+          <t>Unused Security Rule (Policy Optimizer)</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Server Verification Disabled</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.6 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>1.6.1</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>6.3.1</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>VPM-10</t>
-        </is>
-      </c>
+          <t>Unused Rule / Policy Enabled</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>User Credential Submission Uncontrolled</t>
+          <t>Update Server Verification Disabled</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>URL Filtering</t>
+          <t>Server Verification Disabled</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CIS 13.4 · CIS 6.4</t>
+          <t>CIS 4.6 · CIS 12.6</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>6.3.1</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>IAC-06 · NET-04</t>
-        </is>
-      </c>
+          <t>VPM-10</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>User-ID Agent Traffic Unrestricted</t>
+          <t>User Credential Submission Uncontrolled</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Rules Allowing Excessive Traffic</t>
+          <t>URL Filtering</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.3</t>
+          <t>CIS 6.4 · CIS 13.4</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -5110,33 +6285,38 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>IAC-01 · NET-04</t>
-        </is>
-      </c>
+          <t>IAC-06 · NET-04</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>User-ID Enabled on Untrusted Zone</t>
+          <t>User-ID Agent Traffic Unrestricted</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Insecure WMI Probing</t>
+          <t>Rules Allowing Excessive Traffic</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 4.2</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
+          <t>CIS 4.2 · CIS 12.3</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -5144,11 +6324,12 @@
           <t>IAC-01 · NET-04</t>
         </is>
       </c>
+      <c r="H78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>User-ID Network Exclusions Not Configured</t>
+          <t>User-ID Enabled on Untrusted Zone</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -5161,130 +6342,130 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 6.1</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr"/>
+          <t>CIS 4.2 · CIS 12.2</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
           <t>IAC-01 · NET-04</t>
         </is>
       </c>
+      <c r="H79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>User-ID Not Configured</t>
+          <t>User-ID Network Exclusions Not Configured</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>User-ID Is Not Turned On / Configured</t>
+          <t>Insecure WMI Probing</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>CIS 6.1</t>
+          <t>CIS 4.2 · CIS 6.1</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>IAC-01</t>
-        </is>
-      </c>
+          <t>IAC-01 · NET-04</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>VNC Exposed from Any Source</t>
+          <t>User-ID Not Configured</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
+          <t>User-ID Is Not Turned On / Configured</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>1.3.1</t>
-        </is>
-      </c>
+          <t>CIS 6.1</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
-        </is>
-      </c>
+          <t>IAC-01</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability Profile Allows Critical/High Threats</t>
+          <t>VNC Exposed from Any Source</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Threat Protection Missing Or Not Configured</t>
+          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>CIS 13.3 · CIS 13.8</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
+          <t>CIS 12.2 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>6.3.1</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>VPM-01</t>
-        </is>
-      </c>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Vulnerability Profile Not Applied</t>
+          <t>Vulnerability Profile Allows Critical/High Threats</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Missing Security Profile</t>
+          <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5294,7 +6475,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -5307,77 +6488,84 @@
           <t>VPM-01</t>
         </is>
       </c>
+      <c r="H83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WMI Probing Enabled</t>
+          <t>Vulnerability Profile Not Applied</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Insecure WMI Probing</t>
+          <t>Missing Security Profile</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8 · CIS 12.3</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>6.3.1</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>IAC-01 · NET-04</t>
-        </is>
-      </c>
+          <t>VPM-01</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Weak IKE DH Group</t>
+          <t>WMI Probing Enabled</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Weak Cipher Suite</t>
+          <t>Insecure WMI Probing</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>CIS 3.10 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
+          <t>CIS 4.8 · CIS 12.3</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
-        </is>
-      </c>
+          <t>IAC-01 · NET-04</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Weak IKE Encryption</t>
+          <t>Weak IKE DH Group</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -5404,11 +6592,12 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Weak IKE Hash/PRF</t>
+          <t>Weak IKE Encryption</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -5435,11 +6624,12 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Weak IPSec Authentication</t>
+          <t>Weak IKE Hash/PRF</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -5466,11 +6656,12 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Weak IPSec DH Group (PFS)</t>
+          <t>Weak IPSec Authentication</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -5497,11 +6688,12 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Weak IPSec Encryption</t>
+          <t>Weak IPSec DH Group (PFS)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -5528,11 +6720,12 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Weak Minimum TLS Version</t>
+          <t>Weak IPSec Encryption</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -5559,89 +6752,88 @@
           <t>CRY-03</t>
         </is>
       </c>
+      <c r="H91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Weak Password Minimum Length</t>
+          <t>Weak Minimum TLS Version</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Minimum password length</t>
+          <t>Weak Cipher Suite</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>1.3.2</t>
-        </is>
-      </c>
+          <t>CIS 3.10 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>8.3.6</t>
+          <t>4.2.1</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
-        </is>
-      </c>
+          <t>CRY-03</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>WildFire Decrypted Content Not Forwarded</t>
+          <t>Weak Password Minimum Length</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Decrypted Traffic Not Forwarded For Analysis</t>
+          <t>Minimum password length</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.7</t>
+          <t>CIS 5.2</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>1.3.2</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>8.3.6</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
-        </is>
-      </c>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>WildFire File Size Limits Not Maximized</t>
+          <t>WildFire Decrypted Content Not Forwarded</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Threat Protection Missing Or Not Configured</t>
+          <t>Decrypted Traffic Not Forwarded For Analysis</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5651,7 +6843,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5664,11 +6856,12 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>WildFire Inline ML Not Enabled</t>
+          <t>WildFire File Size Limits Not Maximized</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -5686,7 +6879,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -5699,19 +6892,20 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>WildFire Malicious File Alerts Disabled</t>
+          <t>WildFire Inline ML Not Enabled</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Insufficient Logging And Auditing</t>
+          <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5721,7 +6915,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5734,19 +6928,20 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>WildFire Profile Incomplete Coverage</t>
+          <t>WildFire Malicious File Alerts Disabled</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Threat Protection Missing Or Not Configured</t>
+          <t>Insufficient Logging And Auditing</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5754,10 +6949,14 @@
           <t>CIS 10.7</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5765,11 +6964,12 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>WildFire Profile Missing Rules</t>
+          <t>WildFire Profile Incomplete Coverage</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -5796,19 +6996,20 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>WildFire Profile Not Applied</t>
+          <t>WildFire Profile Missing Rules</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Missing Security Profile</t>
+          <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5816,14 +7017,10 @@
           <t>CIS 10.7</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
+      <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.3.2</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -5831,19 +7028,20 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>WildFire Session Information Incomplete</t>
+          <t>WildFire Profile Not Applied</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Threat Protection Missing Or Not Configured</t>
+          <t>Missing Security Profile</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5853,7 +7051,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -5866,19 +7064,20 @@
           <t>TDA-02</t>
         </is>
       </c>
+      <c r="H100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>WildFire Updates Not Automatic</t>
+          <t>WildFire Session Information Incomplete</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>AV/Threat Content Updates Not Automatic</t>
+          <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5888,59 +7087,61 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>5.3.1</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>VPM-10 · TDA-02</t>
-        </is>
-      </c>
+          <t>TDA-02</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Zone Flood Protection Disabled</t>
+          <t>WildFire Updates Not Automatic</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Threat Protection Missing Or Not Configured</t>
+          <t>AV/Threat Content Updates Not Automatic</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>CIS 13.3 · CIS 13.4</t>
+          <t>CIS 10.7</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>6.15 · 6.16</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>5.3.2</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
-        </is>
-      </c>
+          <t>TDA-02 · VPM-10</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Zone Missing Protection Profile</t>
+          <t>Zone Flood Protection Disabled</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -5956,7 +7157,11 @@
           <t>CIS 13.3 · CIS 13.4</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>6.15 · 6.16</t>
+        </is>
+      </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1.2.4 · 1.3.1</t>
@@ -5967,9 +7172,2587 @@
           <t>NET-04</t>
         </is>
       </c>
+      <c r="H103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Zone Missing Protection Profile</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Threat Protection Missing Or Not Configured</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.3 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>1.2.4 · 1.3.1</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G103"/>
+  <autoFilter ref="A1:H104"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Vuln ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Vuln (vulns.txt)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CIS Controls v8</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CIS Check Point Benchmark</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PCI DSS v4.0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SCF</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.1 — Ensure Minimum Password Length is set to 14 or higher</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Minimum password length</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.2 — Ensure Disallow Palindromes is selected</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Password Complexity Requirements Not Enforced</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.3 — Ensure Password Complexity is set to 3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Password Complexity Requirements Not Enforced</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.4 — Ensure Check for Password Reuse is selected and History Length is set to 12 or more - history-checking</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Enforce Password History Missing Or Insufficient</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.5 — Ensure Password Expiration is set to 90 days</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Maximum password age</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.6 — Ensure Warn users before password expiration is set to 7 days</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Maximum password age</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.7 — Ensure Lockout users after password expiration is set to 1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Maximum password age</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>IAC-07</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.8 — Ensure Deny access to unused accounts is selected</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Weak Authentication Configuration</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>IAC-07</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.9 — Ensure Days of non-use before lock-out is set to 30</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Weak Authentication Configuration</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>IAC-07</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.10 — Ensure Force users to change password at first login after password was changed from Users page is selected</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Force Change Password At 1st Login</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.11 — Ensure Deny access after failed login attempts is selected</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Excessive Number Of Failed Login Attempts Allowed</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8.2.8</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.12 — Ensure Maximum number of failed attempts allowed is set to 5 or fewer</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Excessive Number Of Failed Login Attempts Allowed</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8.2.8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CIS 1.13 — Ensure Allow access again after time is set to 300 or more seconds</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Account Lockout Duration Not Configured Or Insufficient</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8.2.8</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>IAC-06</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.1 — Ensure 'Login Banner' is set - message banner on</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Pre Login Banner Not Set</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>IAC-09</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.2 — Ensure 'Message Of The Day (MOTD)' is set - motd banner on</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Post Login Banner Not Set</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2.1.2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>IAC-09</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.3 — Ensure Core Dump is enabled</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2.1.3</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.4 — Ensure Config-state is saved</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2.1.4</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.5 — Ensure unused interfaces are disabled</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Active Interface Not Shutdown</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2.1.5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1.2.1 · 1.4.1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.6 — Ensure DNS server is configured - primary</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DNS Not Configured</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.9</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2.1.6</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.7 — Ensure IPv6 is disabled if not used</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2.1.7</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2.2.3</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.8 — Ensure Host Name is set</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Hostname Not Set</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2.1.8</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.9 — Ensure Telnet is disabled</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Insecure Protocol Use</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2.1.9</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>CRY-03</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.1.10 — Ensure DHCP is disabled</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2.1.10</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.2.1 — Ensure SNMP agent is disabled</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>SNMPv1 Or SNMPv2 Enabled</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 · CIS 12.3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>CRY-03 · NET-06</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.2.2 — Ensure SNMP version is set to v3-Only</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>SNMPv1 Or SNMPv2 Enabled</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.3 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2.2.2</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>CRY-03</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.2.3 — Ensure SNMP traps is enabled - authorizationError</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Logging And Auditing</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2.2.3</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.2.4 — Ensure SNMP traps receivers is set</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Missing Centralized Logging and Reporting</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2 · CIS 8.9</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.3.1 — Ensure NTP is enabled and IP address is set for Primary and Secondary NTP server - ntp active</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>NTP Server Not Configured</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.4</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>10.6 · 10.6.1 · 10.6.2 · 10.6.3</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.3.2 — Ensure timezone is properly configured</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Device Timezone Not Set</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.4</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2.3.2</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.4.1 — Ensure 'System Backup' is set.</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>CIS 11.1</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2.4.1</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>BCD-01</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.4.2 — Ensure 'Snapshot' is set</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>CIS 11.1</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>BCD-01</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.4.3 — Configuring Scheduled Backups</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>CIS 11.2</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>2.4.3</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>BCD-01</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.5.1 — Ensure CLI session timeout is set to less than or equal to 10 minutes</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Session Idle Timeout</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.3</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2.5.1</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>IAC-09</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.5.2 — Ensure Web session timeout is set to less than or equal to 10 minutes</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Session Idle Timeout</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.3</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>2.5.2</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>IAC-09</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.5.3 — Ensure Client Authentication is secured.</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Insecure Protocol Use</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.6</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2.5.3</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>CRY-03</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.5.4 — Ensure Radius or TACACS+ server is configured - tacacs-servers state on</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Weak Authentication Configuration</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.5 · CIS 6.7</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2.5.4</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>IAC-01</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.5.5 — Ensure allowed-client is set to those necessary for device management</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>WAN Management Access</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.7 · CIS 12.3</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2.5.5</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1.3.1 · 1.4.2 · 1.4.3</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>IAC-10 · NET-04</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.6.1 — Ensure mgmtauditlogs is set to on</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Logging And Auditing</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2.6.1</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.6.2 — Ensure auditlog is set to permanent</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Logging And Auditing</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2.6.2</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CIS 2.6.3 — Ensure cplogs is set to on</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Logging And Auditing</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2.6.3</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.1 — Enable the Firewall Stealth Rule</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>WAN Management Access</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1.2.1 · 1.4.1</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.2 — Configure a Default Drop/Cleanup Rule</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Rules Allowing Excessive Traffic</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1.2.1 · 1.3.1 · 1.4.1 · 1.4.2 · 1.4.3</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.3 — Use Checkpoint Sections and Titles</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Missing Rule Description / Comment</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.4 — Ensure Hit count is Enable for the rules</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Unused Rule / Policy Enabled</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.5 — Ensure no Allow Rule with Any in Destination filed present in the Firewall Rules</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.6 — Ensure no Allow Rule with Any in Source filed present in the Firewall Rules</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.7 — Ensure no Allow Rule with Any in Services filed present in the Firewall Rules</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Rules Allowing Excessive Traffic (Any Application Or Any Service)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.8 — Logging should be enable for all Firewall Rules</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Logging And Auditing</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>10.2.2</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.9 — Review and Log Implied Rules</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Logging And Auditing</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2 · CIS 12.2</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10 — Ensure Drop Out of State TCP Packets is enabled</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.11 — Ensure Drop Out of State ICMP Packets is enabled</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.12 — Ensure Anti-Spoofing is enabled and action is set to Prevent for all Interfaces</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.13 — Ensure Disk Space Alert is set</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.14 — Ensure Accept RIP is not enabled</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Insecure Protocol Permitted By Rule / ACL</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.15 — Ensure Accept Domain Name over TCP (Zone Transfer) is not enabled</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Insecure Protocol Permitted By Rule / ACL</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.16 — Ensure Accept Domain Name over UDP (Queries) is not enabled</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Insecure Protocol Permitted By Rule / ACL</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.17 — Ensure Accept ICMP Requests is not enabled</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Insecure Protocol Permitted By Rule / ACL</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.18 — Ensure Allow bi-directional NAT is enabled</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.19 — Ensure Automatic ARP Configuration NAT is enabled</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>(not mapped)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.20 — Ensure Logging is enabled for Track Options of Global Properties</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Logging And Auditing</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>benchmark check</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Disabled Rulebase Rule</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Disabled Rule</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>rulebase check (--rules-csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Missing Rule Comment</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Missing Rule Description / Comment</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>rulebase check (--rules-csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Rule Allows Any Source</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>rulebase check (--rules-csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Rule Allows Any Destination</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>rulebase check (--rules-csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Rule Allows Any Service</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Rules Allowing Excessive Traffic (Any Application Or Any Service)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>rulebase check (--rules-csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Allow Rule Not Logging</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient Logging And Auditing</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>10.2.2</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>rulebase check (--rules-csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>No Hit Count Data</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Unused Rule / Policy Enabled</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>MON-06</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>rulebase check (--rules-csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>No Default Drop/Cleanup Rule</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Rules Allowing Excessive Traffic</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1.2.1 · 1.3.1 · 1.4.1 · 1.4.2 · 1.4.3</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>NET-04</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>rulebase check (--rules-csv)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vulns_framework_mapping.xlsx
+++ b/vulns_framework_mapping.xlsx
@@ -555,7 +555,8 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>MON-11.1
+SEA-30</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -603,7 +604,9 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14
+IAC-14.4
+IAC-15</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -679,7 +682,7 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>AST-03</t>
         </is>
       </c>
     </row>
@@ -703,7 +706,12 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>CFG-08
+NET-04.2</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="n">
         <v>2</v>
       </c>
@@ -726,7 +734,7 @@
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>NET-04.2</t>
         </is>
       </c>
     </row>
@@ -787,8 +795,8 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>CRY-03
-OPS-01</t>
+          <t>CRY-06
+MON-11.1</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -838,8 +846,8 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>TDA-02
-VPM-10</t>
+          <t>THR-04
+VPM-08.1</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -891,8 +899,9 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>CRY-03
-IAC-10</t>
+          <t>CFG-04.7
+CRY-09
+CRY-12</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -939,7 +948,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>CFG-04.1</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -967,7 +976,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>CFG-04.1</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1041,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
@@ -1056,7 +1065,7 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1103,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14.1</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -1123,8 +1132,8 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>IAC-06
-IAC-07</t>
+          <t>IAC-08.4
+IAC-14.1</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1197,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15.1</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1212,7 +1221,7 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15.1</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1285,8 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CFG-03
+CRY-05</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -1311,7 +1321,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1359,8 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>NET-20.1
+NET-42.2</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
@@ -1401,9 +1412,10 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>NET-04
-NET-14
-TDA-02</t>
+          <t>NET-03.9
+NET-17
+NET-31
+THR-04</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -1458,8 +1470,8 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>IAC-06
-NET-04</t>
+          <t>IAC-14.2
+NET-17</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
@@ -1506,7 +1518,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>DAM-01</t>
+          <t>NET-03.5</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
@@ -1587,11 +1599,16 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>CRY-03
-NET-04
-NET-14
-TDA-02
-VPM-01</t>
+          <t>END-04
+END-04.1
+END-04.2
+MON-09
+NET-03.6
+NET-20
+NET-20.1
+NET-21
+NET-31
+NET-42.2</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
@@ -1637,7 +1654,8 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>CFG-04.3
+CFG-04.5</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -1663,7 +1681,7 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>CFG-04.5</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1716,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-05</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
@@ -1723,7 +1741,7 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-05</t>
         </is>
       </c>
     </row>
@@ -1770,8 +1788,9 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>IAC-10
-NET-04</t>
+          <t>NET-03
+NET-04.1
+NET-26.1</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
@@ -1800,7 +1819,7 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1861,8 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03
+NET-04.1</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
@@ -1868,7 +1888,7 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1927,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>CFG-04.1</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -1937,7 +1957,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>CFG-04.1</t>
         </is>
       </c>
     </row>
@@ -1982,7 +2002,9 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14.1
+IAC-15
+IAC-15.1</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
@@ -2008,7 +2030,7 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15.1</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2072,7 @@
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14.1</t>
         </is>
       </c>
     </row>
@@ -2129,9 +2151,10 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>NET-14
-TDA-02
-VPM-01</t>
+          <t>END-04
+NET-03
+NET-31
+NET-42.2</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2194,8 +2217,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>MON-06
-TDA-02</t>
+          <t>MON-04
+MON-05
+MON-05.5
+MON-09
+MON-22.1
+MON-31</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
@@ -2239,8 +2266,11 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MON-06
-NET-04</t>
+          <t>MON-04
+MON-13
+MON-14
+MON-31
+NET-04.2</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2312,9 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04
+CRY-05
+CRY-06</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
@@ -2325,7 +2357,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.2</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
@@ -2367,7 +2399,8 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04
+CRY-05</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
@@ -2409,7 +2442,8 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-08
+NET-04.2</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -2429,7 +2463,8 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-08
+NET-04.2</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2498,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>NET-04.2</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -2488,7 +2523,7 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>NET-04.2</t>
         </is>
       </c>
     </row>
@@ -2522,8 +2557,8 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>CRY-03
-MON-06</t>
+          <t>CRY-05
+MON-12.3</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
@@ -2576,10 +2611,13 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>CRY-01
-IAC-01
-IAC-07
-IAC-10</t>
+          <t>CRY-10
+IAC-03
+IAC-10
+IAC-25
+IAC-30
+IAC-32
+IAC-34</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -2609,8 +2647,9 @@
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>IAC-01
-IAC-07</t>
+          <t>IAC-03
+IAC-08.4
+IAC-32</t>
         </is>
       </c>
     </row>
@@ -2652,8 +2691,8 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>CRY-03
-NET-06</t>
+          <t>CFG-04.7
+CRY-05</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -2684,7 +2723,8 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CFG-04.7
+CRY-05</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2823,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03</t>
         </is>
       </c>
     </row>
@@ -2825,8 +2865,8 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>IAC-01
-NET-04</t>
+          <t>NET-04.1
+NET-09</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -2860,7 +2900,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2968,7 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>SEA-28</t>
         </is>
       </c>
     </row>
@@ -2967,8 +3007,8 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>CRY-03
-MON-06</t>
+          <t>CFG-04.7
+CRY-05</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -3014,7 +3054,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>SEA-28</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
@@ -3038,7 +3078,7 @@
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>SEA-28</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3112,7 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>BCD-22</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -3174,8 +3214,9 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>IAC-10
-NET-04</t>
+          <t>NET-04.1
+NET-06.1
+NET-09</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
@@ -3212,8 +3253,8 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>IAC-10
-NET-04</t>
+          <t>NET-06.1
+NET-09</t>
         </is>
       </c>
     </row>
@@ -3250,8 +3291,8 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>CRY-03
-NET-06</t>
+          <t>CFG-04.7
+CRY-05</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -3283,8 +3324,9 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>CRY-03
-NET-06</t>
+          <t>CFG-03
+CFG-04.7
+CRY-05</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3382,7 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>NET-13</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
@@ -3364,7 +3406,7 @@
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>NET-13</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3440,8 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>MON-11.1
+SEA-30</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
@@ -3429,7 +3472,8 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>MON-11.1
+SEA-30</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3515,7 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>MON-11</t>
         </is>
       </c>
     </row>
@@ -3517,8 +3561,8 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>IAC-01
-NET-04</t>
+          <t>CFG-03
+IAC-14.2</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
@@ -3562,7 +3606,8 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>IAC-30
+NET-04.1</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -3604,7 +3649,8 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>IAC-01</t>
+          <t>IAC-25
+NET-14</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
@@ -3651,7 +3697,8 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>VPM-10</t>
+          <t>CHG-13
+VPM-08.2</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
@@ -3761,7 +3808,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>TDA-02 · VPM-10</t>
+          <t>THR-04 · VPM-08.1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -3793,7 +3840,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14 · IAC-15</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -3829,7 +3876,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · IAC-10</t>
+          <t>CFG-04.7 · CRY-12</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -3861,7 +3908,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>IAC-01</t>
+          <t>IAC-03 · IAC-32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -3897,7 +3944,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>NET-14 · TDA-02</t>
+          <t>END-04.2 · NET-31</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -3929,7 +3976,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-09 · MON-31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -3965,7 +4012,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -4001,7 +4048,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>NET-14 · TDA-02</t>
+          <t>NET-17 · NET-31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -4037,7 +4084,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>END-04</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -4073,7 +4120,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>TDA-02 · VPM-01</t>
+          <t>END-04 · END-04.1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -4105,7 +4152,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>IAC-30 · NET-04.1</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -4137,7 +4184,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03 · NET-04.1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -4169,7 +4216,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CFG-03 · CRY-05</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -4197,7 +4244,7 @@
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>NET-13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -4233,7 +4280,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>DAM-01</t>
+          <t>NET-03.5</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -4269,7 +4316,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-09 · CRY-12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -4305,7 +4352,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-31</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4337,7 +4384,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14.4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4369,7 +4416,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-08 · NET-04.2</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4401,7 +4448,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>IAC-07</t>
+          <t>IAC-10 · IAC-30</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4433,7 +4480,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>IAC-10 · NET-04</t>
+          <t>NET-04.1 · NET-26.1</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -4465,7 +4512,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>END-04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -4501,7 +4548,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · NET-06</t>
+          <t>CFG-04.7 · CRY-05</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -4533,7 +4580,7 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>OPS-04</t>
+          <t>BCD-22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -4569,7 +4616,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-04</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -4601,7 +4648,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>CRY-01</t>
+          <t>CRY-10 · IAC-34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -4633,7 +4680,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -4665,7 +4712,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04 · CRY-05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -4697,7 +4744,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>NET-14</t>
+          <t>NET-03 · NET-31</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -4729,7 +4776,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CFG-03 · CRY-05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -4765,7 +4812,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -4801,7 +4848,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>CFG-04.3 · CFG-04.5</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -4837,7 +4884,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>IAC-10 · NET-04</t>
+          <t>NET-06.1 · NET-09</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -4869,7 +4916,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>NET-04.2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -4901,7 +4948,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>NET-14</t>
+          <t>END-04 · NET-31</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -4933,7 +4980,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · OPS-01</t>
+          <t>CRY-06 · MON-11.1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -4965,7 +5012,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>MON-11.1 · SEA-30</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -4997,7 +5044,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -5029,7 +5076,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -5065,7 +5112,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>CFG-04.1</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -5101,7 +5148,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>CFG-04.1</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5137,7 +5184,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -5169,7 +5216,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -5205,7 +5252,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>SEA-28</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -5237,7 +5284,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>IAC-10 · NET-04</t>
+          <t>NET-06.1 · NET-09</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -5269,7 +5316,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-05</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -5301,7 +5348,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>MON-11.1 · SEA-30</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -5337,7 +5384,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-03.6 · NET-21</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -5373,7 +5420,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15 · IAC-15.1</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -5409,7 +5456,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14.1</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -5445,7 +5492,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14.1 · IAC-15</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -5477,7 +5524,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.2</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -5513,7 +5560,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -5545,7 +5592,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>IAC-01 · IAC-10</t>
+          <t>IAC-25 · IAC-30</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -5577,7 +5624,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-03 · NET-04.1</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -5609,7 +5656,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1 · NET-09</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -5641,7 +5688,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · NET-06</t>
+          <t>CFG-04.7 · CRY-05</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -5673,7 +5720,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · NET-06</t>
+          <t>CFG-04.7 · CRY-05</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -5709,7 +5756,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · MON-06</t>
+          <t>CFG-04.7 · CRY-05</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -5745,7 +5792,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-04 · MON-05</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -5777,7 +5824,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1 · NET-26.1</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -5813,7 +5860,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · NET-14</t>
+          <t>NET-20 · NET-20.1</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -5849,7 +5896,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03 · NET-04.1</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -5881,7 +5928,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · MON-06</t>
+          <t>CRY-05 · MON-12.3</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -5913,7 +5960,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-09 · CRY-12</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -5949,7 +5996,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · NET-06</t>
+          <t>CFG-04.7 · CRY-05</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -5985,7 +6032,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>NET-04 · TDA-02</t>
+          <t>NET-03.9 · THR-04</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -6021,7 +6068,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-17</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -6057,7 +6104,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-17</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -6093,7 +6140,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-22.1</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -6129,7 +6176,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-17</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -6161,7 +6208,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -6193,7 +6240,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -6215,7 +6262,11 @@
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>CFG-08 · NET-04.2</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
@@ -6249,7 +6300,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>VPM-10</t>
+          <t>CHG-13 · VPM-08.2</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -6285,7 +6336,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>IAC-06 · NET-04</t>
+          <t>IAC-14.2 · NET-17</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -6321,7 +6372,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>IAC-01 · NET-04</t>
+          <t>NET-04.1 · NET-09</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -6353,7 +6404,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>IAC-01 · NET-04</t>
+          <t>CFG-03 · IAC-14.2</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -6385,7 +6436,7 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>IAC-01 · NET-04</t>
+          <t>CFG-03 · IAC-14.2</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -6417,7 +6468,7 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>IAC-01</t>
+          <t>IAC-25 · NET-14</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -6449,7 +6500,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1 · NET-26.1</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -6485,7 +6536,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>VPM-01</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -6521,7 +6572,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>VPM-01</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -6557,7 +6608,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>IAC-01 · NET-04</t>
+          <t>CFG-03 · IAC-14.2</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -6589,7 +6640,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04 · CRY-05</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -6621,7 +6672,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04 · CRY-05</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -6653,7 +6704,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04 · CRY-06</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -6685,7 +6736,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04 · CRY-06</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -6717,7 +6768,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04 · CRY-05</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -6749,7 +6800,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04 · CRY-05</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -6781,7 +6832,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CRY-04 · CRY-05</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -6817,7 +6868,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15.1</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -6853,7 +6904,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>NET-20.1 · NET-42.2</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
@@ -6889,7 +6940,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>END-04.2 · NET-42.2</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -6925,7 +6976,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>END-04.2</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -6961,7 +7012,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>MON-05.5</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -6993,7 +7044,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>END-04.2 · NET-42.2</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -7025,7 +7076,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>END-04.2 · NET-42.2</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -7061,7 +7112,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>NET-42.2</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -7097,7 +7148,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>TDA-02</t>
+          <t>MON-09 · NET-42.2</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -7133,7 +7184,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>TDA-02 · VPM-10</t>
+          <t>THR-04 · VPM-08.1</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -7169,7 +7220,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-21</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -7201,7 +7252,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-03.6 · NET-21</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -7300,7 +7351,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15.1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -7336,7 +7387,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15.1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -7372,7 +7423,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15.1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -7408,7 +7459,7 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -7444,7 +7495,7 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14.1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -7480,7 +7531,7 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14.1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7516,7 +7567,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>IAC-07</t>
+          <t>IAC-08.4</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -7552,7 +7603,7 @@
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>IAC-07</t>
+          <t>IAC-08.4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -7588,7 +7639,7 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>IAC-07</t>
+          <t>IAC-08.4</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7624,7 +7675,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>IAC-14.1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -7664,7 +7715,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>CFG-04.1</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -7704,7 +7755,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>CFG-04.1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -7744,7 +7795,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>IAC-06</t>
+          <t>CFG-04.1</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -7780,7 +7831,7 @@
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>SEA-28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -7816,7 +7867,7 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>SEA-28</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -7850,7 +7901,7 @@
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>CFG-04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -7884,7 +7935,7 @@
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>CFG-09</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -7924,7 +7975,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -7960,7 +8011,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>NET-13</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -7998,7 +8049,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -8034,7 +8085,7 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>AST-03</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -8074,7 +8125,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CFG-04.7 · CRY-05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -8112,7 +8163,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -8152,7 +8203,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>CRY-03 · NET-06</t>
+          <t>CFG-03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -8188,7 +8239,7 @@
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CFG-04.7 · CRY-05</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -8224,7 +8275,7 @@
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-04</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -8260,7 +8311,7 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-05</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -8300,7 +8351,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>MON-11.1 · SEA-30</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -8336,7 +8387,7 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>MON-11</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -8370,7 +8421,7 @@
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>BCD-01</t>
+          <t>BCD-24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -8404,7 +8455,7 @@
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>BCD-01</t>
+          <t>BCD-24 · CFG-09</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -8438,7 +8489,7 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>BCD-01</t>
+          <t>BCD-24</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -8474,7 +8525,7 @@
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>CFG-04.5</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -8510,7 +8561,7 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>IAC-09</t>
+          <t>CFG-04.5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -8546,7 +8597,7 @@
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>CRY-03</t>
+          <t>CFG-04.7 · CRY-05</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -8582,7 +8633,7 @@
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>IAC-01</t>
+          <t>IAC-03 · IAC-32</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -8622,7 +8673,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>IAC-10 · NET-04</t>
+          <t>NET-06.1 · NET-09</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -8658,7 +8709,7 @@
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-14</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -8694,7 +8745,7 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-13</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -8730,7 +8781,7 @@
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-04</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -8770,7 +8821,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-09</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -8810,7 +8861,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -8846,7 +8897,7 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>NET-04.2</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -8882,7 +8933,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>NET-04.2</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -8918,7 +8969,7 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -8954,7 +9005,7 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -8990,7 +9041,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -9030,7 +9081,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-31</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -9066,7 +9117,7 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>MON-31 · NET-04.2</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -9100,7 +9151,7 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-03.6</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -9134,7 +9185,7 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-03.6</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -9168,7 +9219,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-03</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -9202,7 +9253,7 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-10.1</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -9238,7 +9289,7 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9274,7 +9325,7 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -9310,7 +9361,7 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -9350,7 +9401,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-03</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -9384,7 +9435,7 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-03.3</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -9418,7 +9469,7 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-03.3</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -9454,7 +9505,7 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-31</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -9486,7 +9537,7 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>CFG-08 · NET-04.2</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -9518,7 +9569,7 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>OPS-01</t>
+          <t>NET-04.2</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -9554,7 +9605,7 @@
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -9590,7 +9641,7 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -9626,7 +9677,7 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -9666,7 +9717,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>MON-31</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -9702,7 +9753,7 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>MON-06</t>
+          <t>NET-04.2</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -9742,7 +9793,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>NET-04</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">

--- a/vulns_framework_mapping.xlsx
+++ b/vulns_framework_mapping.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check Point Findings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'By Vuln'!$A$1:$N$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'By Vuln'!$A$1:$K$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Palo Alto Findings'!$A$1:$H$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Check Point Findings'!$A$1:$H$69</definedName>
   </definedNames>
@@ -434,23 +434,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,32 +463,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>CIS Controls v8</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>PCI DSS v4.0</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SCF 2026.3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t># PA Findings</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Palo Alto Findings</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>PA CIS Controls v8</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>PA CIS Benchmark</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>PA PCI DSS v4.0</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>PA SCF</t>
+          <t>CIS PAN-OS Benchmark</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -506,22 +503,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CP CIS Controls v8</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>CP CIS Benchmark</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>CP PCI DSS v4.0</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>CP SCF</t>
+          <t>CIS Check Point Benchmark</t>
         </is>
       </c>
     </row>
@@ -534,39 +516,37 @@
           <t>Secondary Ntp Server Not Configured</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.4 — Standardize Time Synchronization</t>
+        </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Only One NTP Server</t>
+          <t>PCI 10.6.1 — System clocks are synchronized using time-synchronization technology
+PCI 10.6.2 — Systems are configured to the correct and consistent time</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.4</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>10.6.1</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>MON-11.1
 SEA-30</t>
         </is>
       </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Only One NTP Server</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -577,46 +557,36 @@
           <t>Default Credential Used</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.7 — Manage Default Accounts on Enterprise Assets and Software</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.2 — Vendor default accounts are managed</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>IAC-14.4</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Admin Account Has No Password
 Default/Weak SNMP Community String</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.7
-CIS 5.2
-CIS 6.5
-CIS 12.3</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2.2.4
-8.2.1
-8.3.6</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>IAC-14
-IAC-14.4
-IAC-15</t>
-        </is>
-      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -627,12 +597,24 @@
           <t>Latest Firmware Not Installed</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CIS 7.3 — Perform Automated Operating System Patch Management</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>PCI 6.3.3 — System components are protected from known vulnerabilities by installing security patches</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>VPM-08</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="n">
@@ -640,9 +622,6 @@
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -653,12 +632,24 @@
           <t>Hostname Not Set</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2 — Secure Configuration Process for Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.1 — Configuration standards are defined for all system components</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>AST-03</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="n">
@@ -671,18 +662,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
           <t>2.1.8</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>AST-03</t>
         </is>
       </c>
     </row>
@@ -695,23 +675,30 @@
           <t>Unused Rule / Policy Enabled</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2 — Secure Configuration Process for Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.7 — Configurations of NSCs are reviewed at least once every six months</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>NET-04.2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Unused Security Rule (Policy Optimizer)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>CFG-08
-NET-04.2</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="n">
         <v>2</v>
       </c>
@@ -723,18 +710,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
           <t>3.4</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>NET-04.2</t>
         </is>
       </c>
     </row>
@@ -747,12 +723,24 @@
           <t>Management Using Generic User</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.4 — Restrict Administrator Privileges to Dedicated Accounts</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.2.2 — Group, shared, or generic accounts are used only when necessary and are managed</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>IAC-21</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
@@ -760,9 +748,6 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -773,40 +758,36 @@
           <t>NTP Authentication Not Configured</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.4 — Standardize Time Synchronization</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.6.3 — Time synchronization settings and data are protected</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>MON-11.1
+CRY-06</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>NTP Authentication Not Configured</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.4
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10.6.1</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>CRY-06
-MON-11.1</t>
-        </is>
-      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -817,47 +798,42 @@
           <t>AV/Threat Content Updates Not Automatic</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>CIS 10.2 — Configure Automatic Anti-Malware Signature Updates</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>PCI 5.3.1 — Anti-malware solution is deployed on all applicable system components</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>VPM-08.1</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>AV/Threat Content Updates Not Automatic
 WildFire Updates Not Automatic</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>CIS 10.1
-CIS 10.7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>4.1
 4.2
 5.6</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5.3.2</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>THR-04
-VPM-08.1</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -868,50 +844,43 @@
           <t>Invalid Certificate Used</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10 — Encrypt Sensitive Data in Transit</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PCI 4.2.1 — Strong cryptography is used to safeguard PAN during transmission</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>CRY-09
+CRY-12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Admin Interface Default Certificate
 Decryption Certificate Untrusted
 TLS Profile Using Default Certificate</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10
-CIS 4.2
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1.2.5
 8.3</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2.2.7
-4.2.1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.7
-CRY-09
-CRY-12</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -922,33 +891,32 @@
           <t>Account Lockout Duration Not Configured Or Insufficient</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.4 — Invalid authentication attempts are limited to no more than 10</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>CFG-04.1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>No Account Lockout Policy</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>CIS 5.2
-CIS 6.5</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1.4.1</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8.3.4</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.1</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -961,22 +929,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
           <t>1.13</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8.2.8</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.1</t>
         </is>
       </c>
     </row>
@@ -989,12 +942,24 @@
           <t>Account Lockout Duration Insufficient</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.4 — Invalid authentication attempts are limited to no more than 10</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>CFG-04.1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="n">
@@ -1002,9 +967,6 @@
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1015,35 +977,35 @@
           <t>Enforce Password History Missing Or Insufficient</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.7 — Passwords/passphrases cannot be the same as any of the last four used</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>IAC-15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Insufficient Password History</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1.3.8
 1.3.9</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8.3.7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>IAC-15</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
       </c>
@@ -1054,18 +1016,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
           <t>1.4</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>IAC-15</t>
         </is>
       </c>
     </row>
@@ -1078,32 +1029,32 @@
           <t>Maximum password age</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.9 — Passwords/passphrases for user accounts are changed at least every 90 days</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>IAC-14.1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Password Expiry Not Configured</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1.3.7</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8.3.9</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>IAC-14.1</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -1118,24 +1069,11 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2
-CIS 5.3</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
           <t>1.5
 1.6
 1.7</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>IAC-08.4
-IAC-14.1</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1146,12 +1084,24 @@
           <t>Minimum password age</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.7 — Passwords/passphrases cannot be the same as any of the last four used</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>IAC-15</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="n">
@@ -1159,9 +1109,6 @@
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1172,32 +1119,32 @@
           <t>Minimum password length</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.6 — Passwords/passphrases meet minimum complexity and length requirements</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>IAC-15.1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Weak Password Minimum Length</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1.3.2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8.3.6</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>IAC-15.1</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1210,18 +1157,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
           <t>1.1</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>IAC-15.1</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1170,24 @@
           <t>HA Reserved Management Not Configured</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.3 — Securely Manage Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.1 — Configuration standards are defined for all system components</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>NET-09</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
@@ -1247,9 +1195,6 @@
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1260,35 +1205,34 @@
           <t>Insecure Protocol Permitted By Rule / ACL</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10 — Encrypt Sensitive Data in Transit
+CIS 4.8 — Disable Unnecessary Services on Enterprise Assets and Software</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.6 — Security features are implemented for all insecure services, protocols, and ports in use
+PCI 4.2.1 — Strong cryptography is used to safeguard PAN during transmission</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>CRY-05
+CFG-03</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Cleartext Telnet Allowed
 Insecure Protocol Allowed in Rule</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.8
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2.2.4
-2.2.7
-4.2.1</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>CFG-03
-CRY-05</t>
-        </is>
-      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="n">
         <v>4</v>
       </c>
@@ -1302,28 +1246,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
           <t>3.14
 3.15
 3.16
 3.17</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2.2.4</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>CFG-03</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1334,43 +1262,40 @@
           <t>Decrypted Traffic Not Forwarded For Analysis</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>1</v>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CIS 10.7 — Use Behavior-Based Anti-Malware Software</t>
+        </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>WildFire Decrypted Content Not Forwarded</t>
+          <t>PCI 5.2.2 — The anti-malware solution detects and blocks all known types of malware</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>CIS 10.7</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5.3.1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>NET-20.1
 NET-42.2</t>
         </is>
       </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>WildFire Decrypted Content Not Forwarded</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1381,51 +1306,43 @@
           <t>Block Malicious Domain</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>CIS 9.2 — Use DNS Filtering Services</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PCI 5.2.2 — The anti-malware solution detects and blocks all known types of malware</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>NET-17
+NET-03.9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Anti-Spyware Profile Not Blocking
 Threat Intelligence Blocking Not Configured</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>CIS 10.1
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6.3
 6.24
 7.3</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1.3.1
-5.3.1
-6.3.1</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>NET-03.9
-NET-17
-NET-31
-THR-04</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1436,10 +1353,25 @@
           <t>URL Filtering</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>CIS 9.3 — Maintain and Enforce Network-Based URL Filters</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.3.2 — Outbound traffic from the CDE is restricted to what is necessary</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>NET-17</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>URL Category Action Not Blocking
 URL Filtering Not Configured
@@ -1447,14 +1379,7 @@
 User Credential Submission Uncontrolled</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>CIS 6.4
-CIS 9.2
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>6.8
 6.9
@@ -1462,26 +1387,11 @@
 6.19</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4
-1.3.1</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>IAC-14.2
-NET-17</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1492,33 +1402,32 @@
           <t>Data Filtering</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.13 — Deploy a Data Loss Prevention Solution</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.3.2 — Outbound traffic from the CDE is restricted to what is necessary</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>NET-03.5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Data Filtering Not Applied</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.13
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>6.14</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1.3.2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>NET-03.5</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
@@ -1526,9 +1435,6 @@
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1539,10 +1445,26 @@
           <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.3 — Deploy a Network Intrusion Detection Solution
+CIS 13.8 — Deploy a Network Intrusion Prevention Solution</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>PCI 11.5.1 — Intrusion-detection and/or intrusion-prevention techniques detect and prevent intrusions</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>NET-31</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Advanced Threat Prevention Not Enabled
 Antivirus Profile Not Blocking
@@ -1559,17 +1481,7 @@
 Zone Missing Protection Profile</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10
-CIS 10.1
-CIS 10.7
-CIS 13.3
-CIS 13.4
-CIS 13.8</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>5.1
 5.4
@@ -1587,38 +1499,11 @@
 7.4</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4
-1.3.1
-4.2.1
-5.3.1
-5.3.2
-6.3.1</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>END-04
-END-04.1
-END-04.2
-MON-09
-NET-03.6
-NET-20
-NET-20.1
-NET-21
-NET-31
-NET-42.2</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1629,33 +1514,32 @@
           <t>Insufficient Session Idle Timeout</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.3 — Configure Automatic Session Locking on Enterprise Assets</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.2.8 — If idle for more than 15 minutes, the session re-authenticates the user</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>CFG-04.5</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Long or No Management Session Timeout</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.3</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>1.4.1</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>8.2.8</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.3
-CFG-04.5</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -1669,19 +1553,8 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.3</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
           <t>2.5.1
 2.5.2</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.5</t>
         </is>
       </c>
     </row>
@@ -1694,31 +1567,30 @@
           <t>Missing Centralized Logging and Reporting</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.9 — Centralize Audit Logs</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.3.3 — Audit log files are promptly backed up to a secure, central log server</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>MON-05</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>No Syslog Servers Configured</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.2
-CIS 8.9</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>10.5.4</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>MON-05</t>
-        </is>
-      </c>
+      <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
         <v>1</v>
       </c>
@@ -1729,19 +1601,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2
-CIS 8.9</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
           <t>2.2.4</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>MON-05</t>
         </is>
       </c>
     </row>
@@ -1754,10 +1614,26 @@
           <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4 — Perform Traffic Filtering Between Network Segments</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.3.1 — Inbound traffic to the CDE is restricted to what is necessary
+PCI 1.3.2 — Outbound traffic from the CDE is restricted to what is necessary</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>NET-04.1</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Exposed RDP from Any Source
 Negated Destination Address
@@ -1769,30 +1645,7 @@
 VNC Exposed from Any Source</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2
-CIS 12.2
-CIS 12.3
-CIS 12.6
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4
-1.3.1
-1.3.2</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>NET-03
-NET-04.1
-NET-26.1</t>
-        </is>
-      </c>
+      <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
         <v>4</v>
       </c>
@@ -1806,20 +1659,8 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
           <t>3.5
 3.6</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>NET-04.1</t>
         </is>
       </c>
     </row>
@@ -1832,37 +1673,34 @@
           <t>Rules Allowing Excessive Traffic (Any Application Or Any Service)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4 — Perform Traffic Filtering Between Network Segments</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.5 — All allowed services, protocols, and ports are identified, approved, and have a defined business need</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>NET-04.1
+CFG-03</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Application+Service Both Any
 Service=Any with Specific Application</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2
-CIS 13.4
-CIS 13.10</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>7.2</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4
-1.3.1</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>CFG-03
-NET-04.1</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
@@ -1876,19 +1714,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
           <t>3.7</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>NET-04.1</t>
         </is>
       </c>
     </row>
@@ -1901,33 +1727,32 @@
           <t>Excessive Number Of Failed Login Attempts Allowed</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.4 — Invalid authentication attempts are limited to no more than 10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>CFG-04.1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>No Account Lockout Policy (threshold &gt; 5)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>CIS 5.2
-CIS 6.5</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>1.4.1</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>8.3.4</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.1</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -1941,23 +1766,8 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
           <t>1.11
 1.12</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8.2.8</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.1</t>
         </is>
       </c>
     </row>
@@ -1970,22 +1780,31 @@
           <t>Password Complexity Requirements Not Enforced</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.6 — Passwords/passphrases meet minimum complexity and length requirements</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>IAC-15.1</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Password Complexity Not Enforced
 Password Profile Bypass Configured</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>CIS 5.2
-CIS 6.5</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1.3.1
 1.3.3
@@ -1995,18 +1814,6 @@
 1.3.10</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>8.3.6</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>IAC-14.1
-IAC-15
-IAC-15.1</t>
-        </is>
-      </c>
       <c r="I29" s="2" t="n">
         <v>2</v>
       </c>
@@ -2018,19 +1825,8 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
           <t>1.2
 1.3</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>IAC-15.1</t>
         </is>
       </c>
     </row>
@@ -2043,12 +1839,24 @@
           <t>Force Change Password At 1st Login</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.5 — First-time and reset passwords are unique and changed after first use</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>IAC-14.1</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="n">
@@ -2061,18 +1869,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
           <t>1.10</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>IAC-14.1</t>
         </is>
       </c>
     </row>
@@ -2085,12 +1882,21 @@
           <t>Native VLAN Is The Management VLAN</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 — Establish and Maintain a Secure Network Architecture</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>NET-10
+NET-06.1</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
@@ -2098,9 +1904,6 @@
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2111,10 +1914,28 @@
           <t>Missing Security Profile</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>CIS 10.1 — Deploy and Maintain Anti-Malware Software
+CIS 13.8 — Deploy a Network Intrusion Prevention Solution</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>PCI 5.2.1 — An anti-malware solution is deployed on all applicable system components
+PCI 11.5.1 — Intrusion-detection and/or intrusion-prevention techniques detect and prevent intrusions</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>NET-31
+END-04</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Anti-Spyware Profile Not Applied
 Antivirus Profile Not Applied
@@ -2125,17 +1946,7 @@
 WildFire Profile Not Applied</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>CIS 10.1
-CIS 10.7
-CIS 13.3
-CIS 13.4
-CIS 13.8
-CIS 13.10</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>5.2
 6.2
@@ -2143,28 +1954,11 @@
 6.7</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>5.3.1
-6.3.1</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>END-04
-NET-03
-NET-31
-NET-42.2</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2175,10 +1969,27 @@
           <t>Insufficient Logging And Auditing</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.2 — Collect Audit Logs
+CIS 8.5 — Collect Detailed Audit Logs</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.2.1 — Audit logs are enabled and active for all system components</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>MON-04
+MON-31</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Allow Rule Not Logging Session End
 Default Policy Logging Disabled
@@ -2189,40 +2000,13 @@
 WildFire Malicious File Alerts Disabled</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.2
-CIS 8.5
-CIS 8.9
-CIS 9.2
-CIS 10.7</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>1.1.1.2
 1.1.3
 5.5
 6.10
 7.4</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>5.3.1
-10.2.1
-10.2.2
-10.5.4</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>MON-04
-MON-05
-MON-05.5
-MON-09
-MON-22.1
-MON-31</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
@@ -2242,14 +2026,6 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2
-CIS 8.2
-CIS 8.5
-CIS 12.2</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
           <t>2.2.3
 2.6.1
 2.6.2
@@ -2259,20 +2035,6 @@
 3.20</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>10.2.2</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>MON-04
-MON-13
-MON-14
-MON-31
-NET-04.2</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2283,10 +2045,26 @@
           <t>Weak Cipher Suite</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10 — Encrypt Sensitive Data in Transit</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>PCI 4.2.1 — Strong cryptography is used to safeguard PAN during transmission</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>CRY-04
+CRY-05</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>IKEv1 in Use
 Weak IKE DH Group
@@ -2298,33 +2076,12 @@
 Weak Minimum TLS Version</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>4.2.1</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>CRY-04
-CRY-05
-CRY-06</t>
-        </is>
-      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2335,39 +2092,35 @@
           <t>Shadow Firewall Rule / ACL</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2 — Secure Configuration Process for Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.7 — Configurations of NSCs are reviewed at least once every six months</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>NET-04.2</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Potential Shadow Rule</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2
-CIS 12.2</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>NET-04.2</t>
-        </is>
-      </c>
+      <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2378,39 +2131,36 @@
           <t>PFS Is Disabled</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>1</v>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10 — Encrypt Sensitive Data in Transit</t>
+        </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>IPSec PFS Disabled</t>
+          <t>PCI 4.2.1 — Strong cryptography is used to safeguard PAN during transmission</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>4.2.1</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>CRY-04
 CRY-05</t>
         </is>
       </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>IPSec PFS Disabled</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2421,31 +2171,31 @@
           <t>Disabled Rule</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2 — Secure Configuration Process for Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.7 — Configurations of NSCs are reviewed at least once every six months</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>NET-04.2
+CFG-08</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Disabled Rule</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>CFG-08
-NET-04.2</t>
-        </is>
-      </c>
+      <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
         <v>1</v>
       </c>
@@ -2454,19 +2204,7 @@
           <t>Disabled Rulebase Rule</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>CFG-08
-NET-04.2</t>
-        </is>
-      </c>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2477,30 +2215,30 @@
           <t>Missing Rule Description / Comment</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2 — Secure Configuration Process for Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.5 — All allowed services, protocols, and ports are identified, approved, and have a defined business need</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>NET-04.2</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Missing Rule Description</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>NET-04.2</t>
-        </is>
-      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
         <v>2</v>
       </c>
@@ -2512,18 +2250,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
           <t>3.3</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>NET-04.2</t>
         </is>
       </c>
     </row>
@@ -2536,39 +2263,36 @@
           <t>Syslog Transmitted Over UDP</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10 — Encrypt Sensitive Data in Transit</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.3.2 — Audit log files are protected to prevent modifications</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>MON-12.3
+CRY-05</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Syslog Transmitted Over UDP</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.9</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>10.5.4</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>CRY-05
-MON-12.3</t>
-        </is>
-      </c>
+      <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2579,10 +2303,28 @@
           <t>Weak Authentication Configuration</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.5 — Require MFA for Administrative Access
+CIS 6.7 — Centralize Access Control</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.1 — All user and administrator access is authenticated
+PCI 8.4.1 — MFA is implemented for all non-console administrative access</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>IAC-32
+IAC-14</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Admin Without Authentication Profile
 Excessive Superuser Accounts
@@ -2590,36 +2332,7 @@
 Risky Application Allowed Without User-ID Restriction</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2
-CIS 5.4
-CIS 6.5
-CIS 6.8
-CIS 12.2
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>4.2.1
-7.2.1
-8.2.1
-8.4.1</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>CRY-10
-IAC-03
-IAC-10
-IAC-25
-IAC-30
-IAC-32
-IAC-34</t>
-        </is>
-      </c>
+      <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
         <v>3</v>
       </c>
@@ -2632,26 +2345,11 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.3
-CIS 6.5
-CIS 6.7</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
           <t>1.8
 1.9
 2.5.4</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>IAC-03
-IAC-08.4
-IAC-32</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2662,37 +2360,34 @@
           <t>Insecure Protocol Use</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.6 — Use Secure Network Management and Communication Protocols</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.7 — All non-console administrative access is encrypted</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>CFG-04.7
+CRY-05</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>HTTP Management Enabled
 Telnet Management Enabled</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2
-CIS 12.3
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>1.2.3</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2.2.4
-2.2.7</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.7
-CRY-05</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -2706,25 +2401,8 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
           <t>2.1.9
 2.5.3</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>2.2.4</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.7
-CRY-05</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2415,20 @@
           <t>ARP Inspection Not Enabled</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 — Establish and Maintain a Secure Network Architecture</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>NET-03.6</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="n">
@@ -2750,9 +2436,6 @@
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2763,12 +2446,20 @@
           <t>Spanning Tree (STP) Or Bridge Protocol Data Units (BPDUs) Is Missing</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 — Establish and Maintain a Secure Network Architecture</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>NET-21</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
@@ -2776,9 +2467,6 @@
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2789,12 +2477,24 @@
           <t>Active Interface Not Shutdown</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 — Disable Unnecessary Services on Enterprise Assets and Software</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.4 — Only necessary services, protocols, and functions are enabled</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>CFG-03</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
@@ -2807,23 +2507,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
           <t>2.1.5</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>1.2.1
-1.4.1</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>CFG-03</t>
         </is>
       </c>
     </row>
@@ -2836,37 +2520,34 @@
           <t>Rules Allowing Excessive Traffic</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4 — Perform Traffic Filtering Between Network Segments</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.3.1 — Inbound traffic to the CDE is restricted to what is necessary
+PCI 1.3.2 — Outbound traffic from the CDE is restricted to what is necessary</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>NET-04.1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>No Default Deny Rule
 User-ID Agent Traffic Unrestricted</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2
-CIS 12.2
-CIS 12.3
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2.8</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>NET-04.1
-NET-09</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -2880,27 +2561,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
           <t>3.2</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1.2.1
-1.3.1
-1.4.1
-1.4.2
-1.4.3</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>NET-04.1</t>
         </is>
       </c>
     </row>
@@ -2913,12 +2574,24 @@
           <t>Interface Missing Description</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.4 — Establish and Maintain Architecture Diagram(s)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.3 — An accurate network diagram is maintained</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>AST-17</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
@@ -2926,9 +2599,6 @@
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2939,12 +2609,24 @@
           <t>Post Login Banner Not Set</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2 — Secure Configuration Process for Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.1 — Configuration standards are defined for all system components</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>SEA-28</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
@@ -2957,18 +2639,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
           <t>2.1.2</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>SEA-28</t>
         </is>
       </c>
     </row>
@@ -2981,44 +2652,40 @@
           <t>SNMPv3 Query Per User</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>1</v>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.6 — Use Secure Network Management and Communication Protocols</t>
+        </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>SNMPv3 Polling Not Configured</t>
+          <t>PCI 2.2.7 — All non-console administrative access is encrypted</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.2
-CIS 8.9</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>2.2.4</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>CFG-04.7
 CRY-05</t>
         </is>
       </c>
+      <c r="F48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>SNMPv3 Polling Not Configured</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3029,32 +2696,32 @@
           <t>Pre Login Banner Not Set</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2 — Secure Configuration Process for Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.1 — Configuration standards are defined for all system components</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>SEA-28</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>No Login Banner</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>1.1.2</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>SEA-28</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
@@ -3067,18 +2734,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
           <t>2.1.1</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>SEA-28</t>
         </is>
       </c>
     </row>
@@ -3091,28 +2747,28 @@
           <t>High Availability Not Enabled</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.2 — Establish and Maintain a Secure Network Architecture</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>BCD-22</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>High Availability Not Configured</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>3.1</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>BCD-22</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -3120,9 +2776,6 @@
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3133,12 +2786,25 @@
           <t>Unencrypted Log Traffic</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10 — Encrypt Sensitive Data in Transit</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.3.2 — Audit log files are protected to prevent modifications</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>MON-12.3
+CRY-05</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="n">
@@ -3146,9 +2812,6 @@
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3159,12 +2822,24 @@
           <t>Non-Default Port Usage</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 — Disable Unnecessary Services on Enterprise Assets and Software</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.5 — All allowed services, protocols, and ports are identified, approved, and have a defined business need</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>CFG-03</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
@@ -3172,9 +2847,6 @@
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3185,40 +2857,38 @@
           <t>WAN Management Access</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.3 — Securely Manage Network Infrastructure</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.4.2 — Inbound traffic from untrusted networks to trusted networks is restricted</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>NET-09
+NET-06.1</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Management Interface Not Restricted
 No Management IP Restrictions
 SNMP Enabled Without Source Restrictions</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>CIS 6.7
-CIS 12.3</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>1.2.1
 1.2.2</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>NET-04.1
-NET-06.1
-NET-09</t>
-        </is>
-      </c>
       <c r="I53" s="2" t="n">
         <v>2</v>
       </c>
@@ -3230,31 +2900,8 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>CIS 6.7
-CIS 12.2
-CIS 12.3
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
           <t>2.5.5
 3.1</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>1.2.1
-1.3.1
-1.4.1
-1.4.2
-1.4.3</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>NET-06.1
-NET-09</t>
         </is>
       </c>
     </row>
@@ -3267,34 +2914,32 @@
           <t>SNMPv1 Or SNMPv2 Enabled</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.6 — Use Secure Network Management and Communication Protocols</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.7 — All non-console administrative access is encrypted</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>CFG-04.7
+CRY-05</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>SNMPv1 Enabled
 SNMPv2c Enabled</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2
-CIS 12.3
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>2.2.4</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>CFG-04.7
-CRY-05</t>
-        </is>
-      </c>
+      <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="n">
         <v>2</v>
       </c>
@@ -3306,27 +2951,8 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8
-CIS 12.3
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
           <t>2.2.1
 2.2.2</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>2.2.4</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>CFG-03
-CFG-04.7
-CRY-05</t>
         </is>
       </c>
     </row>
@@ -3339,12 +2965,24 @@
           <t>USB Enabled</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 — Disable Unnecessary Services on Enterprise Assets and Software</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.4 — Only necessary services, protocols, and functions are enabled</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>CFG-05.1</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
@@ -3352,9 +2990,6 @@
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3365,26 +3000,26 @@
           <t>DNS Not Configured</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.9 — Configure Trusted DNS Servers on Enterprise Assets</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>NET-13</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>DNS Not Configured</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.9</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>NET-13</t>
-        </is>
-      </c>
+      <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
         <v>1</v>
       </c>
@@ -3395,18 +3030,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.9</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
           <t>2.1.6</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>NET-13</t>
         </is>
       </c>
     </row>
@@ -3419,31 +3043,31 @@
           <t>NTP Server Not Configured</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>1</v>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.4 — Standardize Time Synchronization</t>
+        </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>NTP Not Configured</t>
+          <t>PCI 10.6.1 — System clocks are synchronized using time-synchronization technology</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.4</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>10.6.1</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>MON-11.1
 SEA-30</t>
         </is>
       </c>
+      <c r="F57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>NTP Not Configured</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="n">
         <v>1</v>
       </c>
@@ -3454,26 +3078,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.4</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
           <t>2.3.1</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>10.6
-10.6.1
-10.6.2
-10.6.3</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>MON-11.1
-SEA-30</t>
         </is>
       </c>
     </row>
@@ -3486,12 +3091,24 @@
           <t>Device Timezone Not Set</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.4 — Standardize Time Synchronization</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.6.2 — Systems are configured to the correct and consistent time</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>MON-11</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
@@ -3504,18 +3121,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.4</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
           <t>2.3.2</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>MON-11</t>
         </is>
       </c>
     </row>
@@ -3528,51 +3134,43 @@
           <t>Insecure WMI Probing</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8 — Disable Unnecessary Services on Enterprise Assets and Software</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.4 — Only necessary services, protocols, and functions are enabled</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>CFG-03
+IAC-14.2</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>User-ID Enabled on Untrusted Zone
 User-ID Network Exclusions Not Configured
 WMI Probing Enabled</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2
-CIS 4.8
-CIS 6.1
-CIS 12.2
-CIS 12.3</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>2.2
 2.4</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>1.3.1
-2.2.4</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>CFG-03
-IAC-14.2</t>
-        </is>
-      </c>
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3583,41 +3181,36 @@
           <t>Rules Allowing Excessive Traffic (Any Source And Any Destination)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4 — Perform Traffic Filtering Between Network Segments</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.3.1 — Inbound traffic to the CDE is restricted to what is necessary
+PCI 1.3.2 — Outbound traffic from the CDE is restricted to what is necessary</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>NET-04.1</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Any/Any/Any Allow Rule</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2
-CIS 13.4</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>1.2.4
-1.3.1</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>IAC-30
-NET-04.1</t>
-        </is>
-      </c>
+      <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -3628,39 +3221,40 @@
           <t>User-ID Is Not Turned On / Configured</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>1</v>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.7 — Centralize Access Control</t>
+        </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>User-ID Not Configured</t>
+          <t>PCI 7.2.1 — All user access is appropriate and access is assigned by business need</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>CIS 6.1</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>IAC-25
 NET-14</t>
         </is>
       </c>
+      <c r="F61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>User-ID Not Configured</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3671,34 +3265,33 @@
           <t>Server Verification Disabled</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.6 — Use Secure Network Management and Communication Protocols</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>PCI 4.2.1 — Strong cryptography is used to safeguard PAN during transmission</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>VPM-08.2
+CHG-13</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Update Server Verification Disabled</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.6
-CIS 12.6</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>1.6.1</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>6.3.1</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>CHG-13
-VPM-08.2</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
@@ -3706,12 +3299,9 @@
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N62"/>
+  <autoFilter ref="A1:K62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3727,11 +3317,11 @@
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3753,14 +3343,14 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>CIS PAN-OS Benchmark</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>CIS Controls v8</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>CIS PAN-OS Benchmark</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PCI DSS v4.0</t>
@@ -3768,7 +3358,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>SCF</t>
+          <t>SCF 2026.3</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -3793,22 +3383,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.1</t>
+          <t>4.1 · 4.2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>4.1 · 4.2</t>
+          <t>CIS 10.2</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>PCI 5.3.1</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>THR-04 · VPM-08.1</t>
+          <t>VPM-08.1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -3827,20 +3417,20 @@
           <t>Default Credential Used</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>CIS 5.2 · CIS 6.5</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.7</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>8.2.1 · 8.3.6</t>
+          <t>PCI 2.2.2</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>IAC-14 · IAC-15</t>
+          <t>IAC-14.4</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -3861,22 +3451,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>CIS 3.10 · CIS 12.6</t>
+          <t>1.2.5</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1.2.5</t>
+          <t>CIS 3.10</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2.2.7 · 4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>CFG-04.7 · CRY-12</t>
+          <t>CRY-09 · CRY-12</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -3895,20 +3485,20 @@
           <t>Weak Authentication Configuration</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>CIS 6.5</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.5 · CIS 6.7</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8.4.1</t>
+          <t>PCI 8.3.1 · PCI 8.4.1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>IAC-03 · IAC-32</t>
+          <t>IAC-32 · IAC-14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -3929,22 +3519,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.1 · CIS 13.4</t>
+          <t>6.22 · 6.23</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6.22 · 6.23</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5.3.1 · 6.3.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>END-04.2 · NET-31</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -3963,20 +3553,20 @@
           <t>Insufficient Logging And Auditing</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>CIS 8.2 · CIS 8.5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10.2.1</t>
+          <t>PCI 10.2.1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>MON-09 · MON-31</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -3997,22 +3587,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.1 · CIS 13.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>CIS 10.1 · CIS 13.8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>PCI 5.2.1 · PCI 11.5.1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>NET-31</t>
+          <t>NET-31 · END-04</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -4033,22 +3623,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.1 · CIS 13.4</t>
+          <t>6.3 · 6.24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6.3 · 6.24</t>
+          <t>CIS 9.2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5.3.1 · 6.3.1</t>
+          <t>PCI 5.2.2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>NET-17 · NET-31</t>
+          <t>NET-17 · NET-03.9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -4069,22 +3659,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.1 · CIS 13.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>CIS 10.1 · CIS 13.8</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>PCI 5.2.1 · PCI 11.5.1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>END-04</t>
+          <t>NET-31 · END-04</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -4105,22 +3695,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.1 · CIS 13.4</t>
+          <t>6.1 · 6.20 · 6.21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6.1 · 6.20 · 6.21</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5.3.1 · 5.3.2</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>END-04 · END-04.1</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -4139,20 +3729,20 @@
           <t>Rules Allowing Excessive Traffic (Any Source And Any Destination)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>IAC-30 · NET-04.1</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -4171,20 +3761,20 @@
           <t>Rules Allowing Excessive Traffic (Any Application Or Any Service)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>CIS 13.4 · CIS 13.10</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>PCI 1.2.5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>CFG-03 · NET-04.1</t>
+          <t>NET-04.1 · CFG-03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -4203,20 +3793,20 @@
           <t>Insecure Protocol Permitted By Rule / ACL</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.8 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 4.8</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2.2.4 · 2.2.7</t>
+          <t>PCI 1.2.6 · PCI 4.2.1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>CFG-03 · CRY-05</t>
+          <t>CRY-05 · CFG-03</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -4235,12 +3825,12 @@
           <t>DNS Not Configured</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>CIS 4.9</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -4265,17 +3855,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CIS 3.13 · CIS 13.4</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>CIS 3.13</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1.3.2</t>
+          <t>PCI 1.3.2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4301,17 +3891,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CIS 3.10 · CIS 12.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>CIS 3.10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4337,22 +3927,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>CIS 8.2 · CIS 8.5</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10.2.1</t>
+          <t>PCI 10.2.1</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>MON-31</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4371,15 +3961,15 @@
           <t>Default Credential Used</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.7 · CIS 12.3</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.7</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>PCI 2.2.2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4403,20 +3993,20 @@
           <t>Disabled Rule</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>CIS 4.2</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.2.7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>CFG-08 · NET-04.2</t>
+          <t>NET-04.2 · CFG-08</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4435,20 +4025,20 @@
           <t>Weak Authentication Configuration</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>CIS 5.4 · CIS 6.8</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.5 · CIS 6.7</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7.2.1</t>
+          <t>PCI 8.3.1 · PCI 8.4.1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>IAC-10 · IAC-30</t>
+          <t>IAC-32 · IAC-14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4467,20 +4057,20 @@
           <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>NET-04.1 · NET-26.1</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -4499,20 +4089,20 @@
           <t>Missing Security Profile</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>CIS 10.1</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>CIS 10.1 · CIS 13.8</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>PCI 5.2.1 · PCI 11.5.1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>END-04</t>
+          <t>NET-31 · END-04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -4533,17 +4123,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.3 · CIS 12.6</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>CIS 12.6</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2.2.4 · 2.2.7</t>
+          <t>PCI 2.2.7</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -4569,12 +4159,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>CIS 12.2</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>3.1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -4601,22 +4191,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2</t>
+          <t>1.1.3</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>CIS 8.2 · CIS 8.5</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10.2.1</t>
+          <t>PCI 10.2.1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>MON-04</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -4635,20 +4225,20 @@
           <t>Weak Authentication Configuration</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.5 · CIS 6.7</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 8.3.1 · PCI 8.4.1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>CRY-10 · IAC-34</t>
+          <t>IAC-32 · IAC-14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -4667,20 +4257,20 @@
           <t>Weak Cipher Suite</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>CRY-04</t>
+          <t>CRY-04 · CRY-05</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -4699,15 +4289,15 @@
           <t>PFS Is Disabled</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>CIS 3.10</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4731,20 +4321,20 @@
           <t>Missing Security Profile</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>CIS 10.1 · CIS 13.4 · CIS 13.8</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>CIS 10.1 · CIS 13.8</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5.3.1 · 6.3.1</t>
+          <t>PCI 5.2.1 · PCI 11.5.1</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>NET-03 · NET-31</t>
+          <t>NET-31 · END-04</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -4763,20 +4353,20 @@
           <t>Insecure Protocol Permitted By Rule / ACL</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.8 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 4.8</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2.2.4 · 4.2.1</t>
+          <t>PCI 1.2.6 · PCI 4.2.1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>CFG-03 · CRY-05</t>
+          <t>CRY-05 · CFG-03</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -4797,17 +4387,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>1.3.8 · 1.3.9</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>1.3.8 · 1.3.9</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8.3.7</t>
+          <t>PCI 8.3.7</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4833,22 +4423,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.3</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>CIS 4.3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>8.2.8</t>
+          <t>PCI 8.2.8</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>CFG-04.3 · CFG-04.5</t>
+          <t>CFG-04.5</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -4869,22 +4459,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CIS 6.7 · CIS 12.3</t>
+          <t>1.2.1 · 1.2.2</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1.2.1 · 1.2.2</t>
+          <t>CIS 12.3</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.4.2</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>NET-06.1 · NET-09</t>
+          <t>NET-09 · NET-06.1</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -4903,15 +4493,15 @@
           <t>Missing Rule Description / Comment</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>CIS 4.2</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.2.5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4935,20 +4525,20 @@
           <t>Missing Security Profile</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>CIS 10.1 · CIS 13.8 · CIS 13.10</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>CIS 10.1 · CIS 13.8</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5.3.1 · 6.3.1</t>
+          <t>PCI 5.2.1 · PCI 11.5.1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>END-04 · NET-31</t>
+          <t>NET-31 · END-04</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -4967,20 +4557,20 @@
           <t>NTP Authentication Not Configured</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.4 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.4</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10.6.1</t>
+          <t>PCI 10.6.3</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>CRY-06 · MON-11.1</t>
+          <t>MON-11.1 · CRY-06</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -4999,15 +4589,15 @@
           <t>NTP Server Not Configured</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>CIS 8.4</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10.6.1</t>
+          <t>PCI 10.6.1</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5031,15 +4621,15 @@
           <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2 · CIS 12.2</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5063,15 +4653,15 @@
           <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2 · CIS 12.2</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5097,17 +4687,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2 · CIS 6.5</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>CIS 5.2</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8.3.4</t>
+          <t>PCI 8.3.4</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5133,17 +4723,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2 · CIS 6.5</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>CIS 5.2</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8.3.4</t>
+          <t>PCI 8.3.4</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5171,15 +4761,15 @@
           <t>Rules Allowing Excessive Traffic</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5203,15 +4793,15 @@
           <t>Insufficient Logging And Auditing</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>CIS 8.2 · CIS 8.5</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10.2.1 · 10.2.2</t>
+          <t>PCI 10.2.1</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5237,17 +4827,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>1.1.2</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.2</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1.1.2</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>PCI 2.2.1</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5271,20 +4861,20 @@
           <t>WAN Management Access</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>CIS 6.7 · CIS 12.3</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.3</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.4.2</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>NET-06.1 · NET-09</t>
+          <t>NET-09 · NET-06.1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -5303,15 +4893,15 @@
           <t>Missing Centralized Logging and Reporting</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.2 · CIS 8.9</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>CIS 8.9</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10.5.4</t>
+          <t>PCI 10.3.3</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5335,15 +4925,15 @@
           <t>Secondary Ntp Server Not Configured</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>CIS 8.4</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10.6.1</t>
+          <t>PCI 10.6.1 · PCI 10.6.2</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5369,22 +4959,22 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>CIS 13.3 · CIS 13.4</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>NET-03.6 · NET-21</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -5405,22 +4995,22 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>1.3.1 · 1.3.3 · 1.3.4 · 1.3.5 · 1.3.6</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>1.3.1 · 1.3.3 · 1.3.4 · 1.3.5 · 1.3.6</t>
-        </is>
-      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8.3.6</t>
+          <t>PCI 8.3.6</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>IAC-15 · IAC-15.1</t>
+          <t>IAC-15.1</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -5441,17 +5031,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>1.3.7</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>1.3.7</t>
-        </is>
-      </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>8.3.9</t>
+          <t>PCI 8.3.9</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5477,22 +5067,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.2 · CIS 6.5</t>
+          <t>1.3.10</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1.3.10</t>
+          <t>CIS 5.2</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8.3.6</t>
+          <t>PCI 8.3.6</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>IAC-14.1 · IAC-15</t>
+          <t>IAC-15.1</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -5511,15 +5101,15 @@
           <t>Shadow Firewall Rule / ACL</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2 · CIS 12.2</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.2.7</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -5545,17 +5135,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CIS 13.3 · CIS 13.4</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -5579,20 +5169,20 @@
           <t>Weak Authentication Configuration</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2 · CIS 12.2</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>CIS 6.5 · CIS 6.7</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7.2.1 · 8.2.1</t>
+          <t>PCI 8.3.1 · PCI 8.4.1</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>IAC-25 · IAC-30</t>
+          <t>IAC-32 · IAC-14</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -5611,20 +5201,20 @@
           <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>NET-03 · NET-04.1</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -5643,20 +5233,20 @@
           <t>WAN Management Access</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>CIS 6.7 · CIS 12.3</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.3</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.4.2</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>NET-04.1 · NET-09</t>
+          <t>NET-09 · NET-06.1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -5675,15 +5265,15 @@
           <t>SNMPv1 Or SNMPv2 Enabled</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2 · CIS 12.3 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.6</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>PCI 2.2.7</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -5707,15 +5297,15 @@
           <t>SNMPv1 Or SNMPv2 Enabled</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2 · CIS 12.3</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>CIS 12.6</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>PCI 2.2.7</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -5741,17 +5331,17 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2 · CIS 8.9</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>CIS 12.6</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>PCI 2.2.7</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -5777,22 +5367,22 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2 · CIS 8.9</t>
+          <t>1.1.1.2</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1.1.1.2</t>
+          <t>CIS 8.2 · CIS 8.5</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>10.2.1 · 10.5.4</t>
+          <t>PCI 10.2.1</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>MON-04 · MON-05</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -5811,20 +5401,20 @@
           <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2 · CIS 12.3</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>NET-04.1 · NET-26.1</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -5845,22 +5435,22 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>CIS 3.10 · CIS 13.4</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>NET-20 · NET-20.1</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -5881,22 +5471,22 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>CIS 13.4</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.2.5</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>CFG-03 · NET-04.1</t>
+          <t>NET-04.1 · CFG-03</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -5915,20 +5505,20 @@
           <t>Syslog Transmitted Over UDP</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>CIS 8.9</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>10.5.4</t>
+          <t>PCI 10.3.2</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>CRY-05 · MON-12.3</t>
+          <t>MON-12.3 · CRY-05</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -5947,15 +5537,15 @@
           <t>Invalid Certificate Used</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -5981,17 +5571,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.3 · CIS 12.6</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>CIS 12.6</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2.2.4 · 2.2.7</t>
+          <t>PCI 2.2.7</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -6017,22 +5607,22 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.1 · CIS 13.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>CIS 9.2</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>PCI 5.2.2</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>NET-03.9 · THR-04</t>
+          <t>NET-17 · NET-03.9</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -6053,17 +5643,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CIS 9.2 · CIS 13.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>CIS 9.3</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>PCI 1.3.2</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -6089,17 +5679,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CIS 9.2 · CIS 13.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>CIS 9.3</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>PCI 1.3.2</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -6125,22 +5715,22 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2 · CIS 9.2</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>CIS 8.2 · CIS 8.5</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>10.2.1</t>
+          <t>PCI 10.2.1</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>MON-22.1</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -6161,17 +5751,17 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CIS 9.2 · CIS 13.4</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>CIS 9.3</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>PCI 1.3.2</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -6195,15 +5785,15 @@
           <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1.3.2</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6227,15 +5817,15 @@
           <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -6260,11 +5850,19 @@
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.7</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>CFG-08 · NET-04.2</t>
+          <t>NET-04.2</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -6285,22 +5883,22 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.6 · CIS 12.6</t>
+          <t>1.6.1</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1.6.1</t>
+          <t>CIS 12.6</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>6.3.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>CHG-13 · VPM-08.2</t>
+          <t>VPM-08.2 · CHG-13</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -6321,22 +5919,22 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>CIS 6.4 · CIS 13.4</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>CIS 9.3</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.3.2</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>IAC-14.2 · NET-17</t>
+          <t>NET-17</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -6357,22 +5955,22 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.3</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>CIS 13.4</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>NET-04.1 · NET-09</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -6391,15 +5989,15 @@
           <t>Insecure WMI Probing</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>CIS 4.2 · CIS 12.2</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>CIS 4.8</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>PCI 2.2.4</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6425,15 +6023,19 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 6.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
+          <t>CIS 4.8</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.4</t>
+        </is>
+      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>CFG-03 · IAC-14.2</t>
@@ -6457,15 +6059,19 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>CIS 6.1</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
+          <t>CIS 6.7</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>PCI 7.2.1</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
           <t>IAC-25 · NET-14</t>
@@ -6487,20 +6093,20 @@
           <t>Rules Allowing Excessive Traffic (Any Source Or Any Destination)</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>CIS 12.2 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>NET-04.1 · NET-26.1</t>
+          <t>NET-04.1</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -6521,17 +6127,17 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>6.3.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6557,22 +6163,22 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>CIS 13.3 · CIS 13.8</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>CIS 10.1 · CIS 13.8</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>6.3.1</t>
+          <t>PCI 5.2.1 · PCI 11.5.1</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>NET-31</t>
+          <t>NET-31 · END-04</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -6593,17 +6199,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8 · CIS 12.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>CIS 4.8</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>PCI 2.2.4</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -6627,15 +6233,15 @@
           <t>Weak Cipher Suite</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -6659,15 +6265,15 @@
           <t>Weak Cipher Suite</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -6691,20 +6297,20 @@
           <t>Weak Cipher Suite</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>CRY-04 · CRY-06</t>
+          <t>CRY-04 · CRY-05</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -6723,20 +6329,20 @@
           <t>Weak Cipher Suite</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>CRY-04 · CRY-06</t>
+          <t>CRY-04 · CRY-05</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -6755,15 +6361,15 @@
           <t>Weak Cipher Suite</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -6787,15 +6393,15 @@
           <t>Weak Cipher Suite</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -6819,15 +6425,15 @@
           <t>Weak Cipher Suite</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>CIS 3.10 · CIS 12.6</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>CIS 3.10</t>
+        </is>
+      </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>4.2.1</t>
+          <t>PCI 4.2.1</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -6853,17 +6459,17 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
+          <t>1.3.2</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>1.3.2</t>
-        </is>
-      </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>8.3.6</t>
+          <t>PCI 8.3.6</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -6889,17 +6495,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>CIS 10.7</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>PCI 5.2.2</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -6925,22 +6531,22 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>END-04.2 · NET-42.2</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -6961,22 +6567,22 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>END-04.2</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -6997,22 +6603,22 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>CIS 8.2 · CIS 8.5</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>PCI 10.2.1</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>MON-05.5</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -7031,20 +6637,20 @@
           <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>CIS 10.7</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.3 · CIS 13.8</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>END-04.2 · NET-42.2</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -7063,20 +6669,20 @@
           <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>CIS 10.7</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.3 · CIS 13.8</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>END-04.2 · NET-42.2</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -7097,22 +6703,22 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.7</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>CIS 10.1 · CIS 13.8</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>PCI 5.2.1 · PCI 11.5.1</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>NET-42.2</t>
+          <t>NET-31 · END-04</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -7133,22 +6739,22 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>MON-09 · NET-42.2</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -7169,22 +6775,22 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>CIS 10.7</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>CIS 10.2</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>5.3.2</t>
+          <t>PCI 5.3.1</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>THR-04 · VPM-08.1</t>
+          <t>VPM-08.1</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -7205,22 +6811,22 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>CIS 13.3 · CIS 13.4</t>
+          <t>6.15 · 6.16</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>6.15 · 6.16</t>
+          <t>CIS 13.3 · CIS 13.8</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>NET-21</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -7239,20 +6845,20 @@
           <t>Threat Protection Missing Or Not Configured</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>CIS 13.3 · CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>CIS 13.3 · CIS 13.8</t>
+        </is>
+      </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>1.2.4 · 1.3.1</t>
+          <t>PCI 11.5.1</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>NET-03.6 · NET-21</t>
+          <t>NET-31</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -7274,11 +6880,11 @@
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -7300,14 +6906,14 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>CIS Check Point Benchmark</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>CIS Controls v8</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>CIS Check Point Benchmark</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PCI DSS v4.0</t>
@@ -7315,7 +6921,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>SCF</t>
+          <t>SCF 2026.3</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -7340,15 +6946,19 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.6</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>IAC-15.1</t>
@@ -7376,15 +6986,19 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.6</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>IAC-15.1</t>
@@ -7412,15 +7026,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.6</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>IAC-15.1</t>
@@ -7448,15 +7066,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.7</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>IAC-15</t>
@@ -7484,15 +7106,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.9</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>IAC-14.1</t>
@@ -7520,15 +7146,19 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.9</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>IAC-14.1</t>
@@ -7556,18 +7186,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.3</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>CIS 5.2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.9</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>IAC-08.4</t>
+          <t>IAC-14.1</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -7592,18 +7226,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+          <t>CIS 6.5 · CIS 6.7</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.1 · PCI 8.4.1</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>IAC-08.4</t>
+          <t>IAC-32 · IAC-14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -7628,18 +7266,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CIS 5.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>CIS 6.5 · CIS 6.7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.1 · PCI 8.4.1</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>IAC-08.4</t>
+          <t>IAC-32 · IAC-14</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7664,15 +7306,19 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.5</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>IAC-14.1</t>
@@ -7700,17 +7346,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8.2.8</t>
+          <t>PCI 8.3.4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7740,17 +7386,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8.2.8</t>
+          <t>PCI 8.3.4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7780,17 +7426,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>CIS 5.2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8.2.8</t>
+          <t>PCI 8.3.4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7820,15 +7466,19 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.2</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2.1.1</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.1</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>SEA-28</t>
@@ -7856,15 +7506,19 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2.1.2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2.1.2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.1</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>SEA-28</t>
@@ -7885,17 +7539,17 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>2.1.3</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2.1.3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -7919,17 +7573,17 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>2.1.4</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.2</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2.1.4</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -7960,17 +7614,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>2.1.5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.8</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2.1.5</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1.2.1 · 1.4.1</t>
+          <t>PCI 2.2.4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8000,12 +7654,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>2.1.6</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.9</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2.1.6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -8029,22 +7683,22 @@
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>2.1.7</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.8</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>2.1.7</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>PCI 2.2.3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8074,15 +7728,19 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>2.1.8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2.1.8</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.1</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>AST-03</t>
@@ -8110,17 +7768,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8 · CIS 12.6</t>
+          <t>2.1.9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2.1.9</t>
+          <t>CIS 12.6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>PCI 2.2.7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8143,22 +7801,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>2.1.10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.8</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2.1.10</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>PCI 2.2.4</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8188,22 +7846,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8 · CIS 12.3</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>CIS 12.6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>PCI 2.2.7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>CFG-03</t>
+          <t>CFG-04.7 · CRY-05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -8228,15 +7886,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.3 · CIS 12.6</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2.2.2</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>CIS 12.6</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.7</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>CFG-04.7 · CRY-05</t>
@@ -8264,18 +7926,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2.2.3</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.2.1</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>MON-04</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -8300,15 +7966,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2 · CIS 8.9</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t>CIS 8.9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.3.3</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>MON-05</t>
@@ -8336,17 +8006,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>CIS 8.4</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>2.3.1</t>
-        </is>
-      </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10.6 · 10.6.1 · 10.6.2 · 10.6.3</t>
+          <t>PCI 10.6.1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8376,15 +8046,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>2.3.2</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>CIS 8.4</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2.3.2</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.6.2</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>MON-11</t>
@@ -8405,17 +8079,17 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>2.4.1</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>CIS 11.1</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>2.4.1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
@@ -8439,17 +8113,17 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>CIS 11.1</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2.4.2</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
@@ -8473,17 +8147,17 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>2.4.3</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>CIS 11.2</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>2.4.3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
@@ -8514,15 +8188,19 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.3</t>
+          <t>2.5.1</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2.5.1</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>CIS 4.3</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.2.8</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>CFG-04.5</t>
@@ -8550,15 +8228,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.3</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2.5.2</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
+          <t>CIS 4.3</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.2.8</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>CFG-04.5</t>
@@ -8586,15 +8268,19 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>2.5.3</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>CIS 12.6</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>2.5.3</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>PCI 2.2.7</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>CFG-04.7 · CRY-05</t>
@@ -8622,18 +8308,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>2.5.4</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>CIS 6.5 · CIS 6.7</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>2.5.4</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>PCI 8.3.1 · PCI 8.4.1</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>IAC-03 · IAC-32</t>
+          <t>IAC-32 · IAC-14</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -8658,22 +8348,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CIS 6.7 · CIS 12.3</t>
+          <t>2.5.5</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2.5.5</t>
+          <t>CIS 12.3</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1.3.1 · 1.4.2 · 1.4.3</t>
+          <t>PCI 1.4.2</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>NET-06.1 · NET-09</t>
+          <t>NET-09 · NET-06.1</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -8698,18 +8388,22 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2</t>
+          <t>2.6.1</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2.6.1</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.2.1</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>MON-14</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -8734,18 +8428,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.5</t>
+          <t>2.6.2</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2.6.2</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.2.1</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>MON-13</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -8770,18 +8468,22 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2</t>
+          <t>2.6.3</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2.6.3</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.2.1</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>MON-04</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -8806,22 +8508,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>CIS 12.3</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1.2.1 · 1.4.1</t>
+          <t>PCI 1.4.2</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>NET-09</t>
+          <t>NET-09 · NET-06.1</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -8846,17 +8548,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>CIS 13.4</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1.2.1 · 1.3.1 · 1.4.1 · 1.4.2 · 1.4.3</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -8886,15 +8588,19 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>CIS 4.2</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.5</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>NET-04.2</t>
@@ -8922,15 +8628,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.7</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>NET-04.2</t>
@@ -8958,15 +8668,19 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>NET-04.1</t>
@@ -8994,15 +8708,19 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
           <t>NET-04.1</t>
@@ -9030,18 +8748,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.5</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>NET-04.1</t>
+          <t>NET-04.1 · CFG-03</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -9066,22 +8788,22 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>CIS 8.2 · CIS 8.5</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>10.2.2</t>
+          <t>PCI 10.2.1</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>MON-31</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -9106,18 +8828,22 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.2 · CIS 12.2</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.2.1</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>MON-31 · NET-04.2</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -9135,17 +8861,17 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>3.10</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -9169,17 +8895,17 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>3.11</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -9203,17 +8929,17 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>CIS 13.4</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>3.12</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -9237,17 +8963,17 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>CIS 8.2</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>3.13</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -9278,18 +9004,22 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8 · CIS 13.4</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
+          <t>CIS 3.10 · CIS 4.8</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.6 · PCI 4.2.1</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>CFG-03</t>
+          <t>CRY-05 · CFG-03</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -9314,18 +9044,22 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8 · CIS 13.4</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
+          <t>CIS 3.10 · CIS 4.8</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.6 · PCI 4.2.1</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>CFG-03</t>
+          <t>CRY-05 · CFG-03</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -9350,18 +9084,22 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8 · CIS 13.4</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3.16</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
+          <t>CIS 3.10 · CIS 4.8</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.6 · PCI 4.2.1</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>CFG-03</t>
+          <t>CRY-05 · CFG-03</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -9386,22 +9124,22 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CIS 4.8 · CIS 13.4</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>CIS 3.10 · CIS 4.8</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>PCI 1.2.6 · PCI 4.2.1</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>CFG-03</t>
+          <t>CRY-05 · CFG-03</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -9419,17 +9157,17 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>CIS 12.2</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>3.18</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -9453,17 +9191,17 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>(not mapped)</t>
+          <t>(not mapped — own framework mapping)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>CIS 12.2</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>3.19</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -9494,18 +9232,22 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>PCI 10.2.1</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>MON-31</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -9528,16 +9270,20 @@
           <t>Disabled Rule</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>CIS 4.2</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.7</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>CFG-08 · NET-04.2</t>
+          <t>NET-04.2 · CFG-08</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -9560,13 +9306,17 @@
           <t>Missing Rule Description / Comment</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>CIS 4.2</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.5</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>NET-04.2</t>
@@ -9594,15 +9344,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>NET-04.1</t>
@@ -9630,15 +9384,19 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>NET-04.1</t>
@@ -9666,18 +9424,22 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
+          <t>CIS 13.4</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.5</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>NET-04.1</t>
+          <t>NET-04.1 · CFG-03</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -9702,22 +9464,22 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>CIS 8.2 · CIS 8.5</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>10.2.2</t>
+          <t>PCI 10.2.1</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>MON-31</t>
+          <t>MON-04 · MON-31</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -9742,15 +9504,19 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CIS 8.2</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>PCI 1.2.7</t>
+        </is>
+      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>NET-04.2</t>
@@ -9778,17 +9544,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CIS 12.2 · CIS 13.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>CIS 13.4</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>1.2.1 · 1.3.1 · 1.4.1 · 1.4.2 · 1.4.3</t>
+          <t>PCI 1.3.1 · PCI 1.3.2</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
